--- a/price-tracking/channels/alkhater/alkhater_ac_prices.xlsx
+++ b/price-tracking/channels/alkhater/alkhater_ac_prices.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-05-11 12:34</t>
+          <t>2026-05-11 12:50</t>
         </is>
       </c>
     </row>

--- a/price-tracking/channels/alkhater/alkhater_ac_prices.xlsx
+++ b/price-tracking/channels/alkhater/alkhater_ac_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N177"/>
+  <dimension ref="A1:N172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “DGS18C مكيف دان سات 18000 وحدة بارد جداري واي فاي”</t>
+          <t>“DGS18C مكيف دان سات 18000 وحدة بارد جداري واي فاي”</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف نيكاى 1.5 طن 18000 وحدة بارد شباك - NWAC18056C25”</t>
+          <t>“مكيف نيكاى 1.5 طن 18000 وحدة بارد شباك - NWAC18056C25”</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “نيكاي مكيف 18000 وحدة , 1.5 طن سبلت , بارد - NSAC18136C25S”</t>
+          <t>“نيكاي مكيف 18000 وحدة , 1.5 طن سبلت , بارد - NSAC18136C25S”</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف كرفت جداري 12100 وحدة بارد انفيرتر - DW12E6AA3IXS00/DT12E6YG3IXS00”</t>
+          <t>“مكيف كرفت جداري 12100 وحدة بارد انفيرتر - DW12E6AA3IXS00/DT12E6YG3IXS00”</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جنرال دان شباك 17200 وحدة 1.5 طن - بارد - GD18WCA”</t>
+          <t>“مكيف جنرال دان شباك 17200 وحدة 1.5 طن - بارد - GD18WCA”</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “ماندو بلس مكيف هواء سبليت مع تحكم واي فاي - 22000 وحدة بارد - MP-NF23-24C”</t>
+          <t>“ماندو بلس مكيف هواء سبليت مع تحكم واي فاي - 22000 وحدة بارد - MP-NF23-24C”</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف هوم كوين سبليت 12000 وحدة ذاتي التنظيف – WIFI – بارد - HQAS120CN”</t>
+          <t>“مكيف هوم كوين سبليت 12000 وحدة ذاتي التنظيف – WIFI – بارد - HQAS120CN”</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “اس كي ام SKM 18000 وحدة مكيف هواء سبيلت بارد - ابيض،- MSKMP-18CWMCD0”</t>
+          <t>“اس كي ام SKM 18000 وحدة مكيف هواء سبيلت بارد - ابيض،- MSKMP-18CWMCD0”</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف ماندو بلس 18300 وحدة 1.5 طن - بارد جداري - MP-NF23-18C”</t>
+          <t>“مكيف ماندو بلس 18300 وحدة 1.5 طن - بارد جداري - MP-NF23-18C”</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “UW12CRHT00 مكيف روود 12300 وحدة انفيرتر حار بارد جداري”</t>
+          <t>“UW12CRHT00 مكيف روود 12300 وحدة انفيرتر حار بارد جداري”</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “GWC12AGC-D3NTA1A - مكيف جري بولار 11600 وحدة بارد جداري واي فاي”</t>
+          <t>“GWC12AGC-D3NTA1A - مكيف جري بولار 11600 وحدة بارد جداري واي فاي”</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف دانسات 18000 وحدة , 1.5 طن , بارد - جداري - DSA18MC”</t>
+          <t>“مكيف دانسات 18000 وحدة , 1.5 طن , بارد - جداري - DSA18MC”</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “كرفت مكيف 12100 وحدة  1 طن بارد  - سبلت - انفيرتر - CSAC12FE6T/CSAC12CE6T”</t>
+          <t>“كرفت مكيف 12100 وحدة  1 طن بارد  - سبلت - انفيرتر - CSAC12FE6T/CSAC12CE6T”</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف فريجو جلاكسي جداري بارد 21600 وحدة - FW24X2G”</t>
+          <t>“مكيف فريجو جلاكسي جداري بارد 21600 وحدة - FW24X2G”</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “HW-18LME13/R2(T3) مكيف هاير شباك 17200 وحده بارد”</t>
+          <t>“HW-18LME13/R2(T3) مكيف هاير شباك 17200 وحده بارد”</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “ZCP18CRXFMKTW مكيف الزامل شباك 18000 وحدة بارد”</t>
+          <t>“ZCP18CRXFMKTW مكيف الزامل شباك 18000 وحدة بارد”</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “هاير شباك 21500 وحدة, روتاري, بارد فقط - HW-24LWA13/R2(T3)”</t>
+          <t>“هاير شباك 21500 وحدة, روتاري, بارد فقط - HW-24LWA13/R2(T3)”</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “ميديا مكيف شباك 18000 وحدة - بارد فقط - انفيرتر - أبيض - WDV18CWG”</t>
+          <t>“ميديا مكيف شباك 18000 وحدة - بارد فقط - انفيرتر - أبيض - WDV18CWG”</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف الزامل شباك 21600 وحدة بارد  - ZCP24CRXFMKHW”</t>
+          <t>“مكيف الزامل شباك 21600 وحدة بارد  - ZCP24CRXFMKHW”</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “FW18X2Gمكيف فريجو 18000 وحدة بارد جداري”</t>
+          <t>“FW18X2Gمكيف فريجو 18000 وحدة بارد جداري”</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “جري مكيف هواء سبليت مع تحكم واي فاي - 32200 وحدة - بارد فقط - GWC36QFXH-D3NTB4B”</t>
+          <t>“جري مكيف هواء سبليت مع تحكم واي فاي - 32200 وحدة - بارد فقط - GWC36QFXH-D3NTB4B”</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “جري مكيف هواء سبليت مع تحكم واي فاي - 28000 وحدة - بارد فقط - GWC30AGEXH-D3NTA1A”</t>
+          <t>“جري مكيف هواء سبليت مع تحكم واي فاي - 28000 وحدة - بارد فقط - GWC30AGEXH-D3NTA1A”</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف TCL تي سي ال  1.5 طن , 18000 وحدة , بارد - شباك - CW-TW18CW1S”</t>
+          <t>“مكيف TCL تي سي ال  1.5 طن , 18000 وحدة , بارد - شباك - CW-TW18CW1S”</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5196,10 +5196,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “TH-X12BHK مكيف توريندو 12000 وحدة بارد جداري”</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>“TH-X12BHK مكيف توريندو 12000 وحدة بارد جداري”</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Tornado</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>TH-X12BHK</t>
@@ -5254,7 +5258,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف روود 18000 وحدة 1.5 طن بارد فقط سبلت - UW18CRCT01”</t>
+          <t>“مكيف روود 18000 وحدة 1.5 طن بارد فقط سبلت - UW18CRCT01”</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5316,7 +5320,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “HSU-12LPB13/R2(T3) مكيف هاير 12400 وحدة بارد جداري”</t>
+          <t>“HSU-12LPB13/R2(T3) مكيف هاير 12400 وحدة بارد جداري”</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5378,7 +5382,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “نيكاي مكيف 21000 وحدة , 2 طن بارد سبلت - NSAC24136C24”</t>
+          <t>“نيكاي مكيف 21000 وحدة , 2 طن بارد سبلت - NSAC24136C24”</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5440,7 +5444,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف الزامل 2 طن 22200 وحدة بارد جداري - HAZ24CCXRDK-HRZ24CDBCIRDK”</t>
+          <t>“مكيف الزامل 2 طن 22200 وحدة بارد جداري - HAZ24CCXRDK-HRZ24CDBCIRDK”</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5502,7 +5506,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “FT18X2GH مكيف فريجو شباك 17200 وحدة بارد”</t>
+          <t>“FT18X2GH مكيف فريجو شباك 17200 وحدة بارد”</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5564,7 +5568,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “AF-W18BHK مكيف تورنيدو شباك 18000 وحدة”</t>
+          <t>“AF-W18BHK مكيف تورنيدو شباك 18000 وحدة”</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5626,7 +5630,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “WDV24CWG - مكيف ميديا شباك 20500 وحدة بارد انفيرتر”</t>
+          <t>“WDV24CWG - مكيف ميديا شباك 20500 وحدة بارد انفيرتر”</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5688,10 +5692,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “كرافت مكيف شباك 18000 وحدة , 1.5 طن , بارد  - CWACH18C”</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>“كرافت مكيف شباك 18000 وحدة , 1.5 طن , بارد  - CWACH18C”</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Crafft</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>CWACH18C</t>
@@ -5746,7 +5754,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “هاير مكيف جداري 33000 وحدة 3 طن , حار / بارد , انفرتر , واي فاي , أبيض - HSU-36HPA13/R2”</t>
+          <t>“هاير مكيف جداري 33000 وحدة 3 طن , حار / بارد , انفرتر , واي فاي , أبيض - HSU-36HPA13/R2”</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5808,7 +5816,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “FT24X2GH مكيف فريجو شباك 21500 وحدة بارد”</t>
+          <t>“FT24X2GH مكيف فريجو شباك 21500 وحدة بارد”</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5870,7 +5878,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف سوبر جنرال 18000 وحدة بارد شباك - KSGA19GE1”</t>
+          <t>“مكيف سوبر جنرال 18000 وحدة بارد شباك - KSGA19GE1”</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5932,7 +5940,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري كوزمو 33000 وحدة بارد جداري - GWC36AWFXH-D6NTA1A”</t>
+          <t>“مكيف جري كوزمو 33000 وحدة بارد جداري - GWC36AWFXH-D6NTA1A”</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5994,7 +6002,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري بولار سبليت مع تحكم واي فاي - 28000 وحدة - حار بارد -  GWH30AGE-D3NTA1A”</t>
+          <t>“مكيف جري بولار سبليت مع تحكم واي فاي - 28000 وحدة - حار بارد -  GWH30AGE-D3NTA1A”</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6056,7 +6064,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “كرفت مكيف 22000 وحدة بارد 2 طن - سبلت - CSAC24FE6T/CSAC24CE6T”</t>
+          <t>“كرفت مكيف 22000 وحدة بارد 2 طن - سبلت - CSAC24FE6T/CSAC24CE6T”</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6118,7 +6126,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “كرفت مكيف 18000 وحدة بارد 1.5 طن - سبلت - CSAC18FE6T/CSAC18CE6T”</t>
+          <t>“كرفت مكيف 18000 وحدة بارد 1.5 طن - سبلت - CSAC18FE6T/CSAC18CE6T”</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6175,21 +6183,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AC06666</t>
+          <t>AC07654</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “خدمة تركيب مكيف اسبليت - AC06666”</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>“مكيف  تورنيدو 18000 وحدة بارد جداري - TH-C18AHK/TU-C18AHK”</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tornado</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>AC06666</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>TH-C18AHK</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -6206,17 +6220,17 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>199</v>
+        <v>2399</v>
       </c>
       <c r="J94" t="n">
-        <v>199</v>
+        <v>2399</v>
       </c>
       <c r="K94" t="b">
         <v>0</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d8%ae%d8%af%d9%85%d8%a9-%d8%aa%d8%b1%d9%83%d9%8a%d8%a8-%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-ac06666/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%aa%d9%88%d8%b1%d9%86%d9%8a%d8%af%d9%88-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-th-c18ahk-tu-c18ahk/</t>
         </is>
       </c>
       <c r="M94" t="n">
@@ -6231,27 +6245,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AC07654</t>
+          <t>AC08598</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف  تورنيدو 18000 وحدة بارد جداري - TH-C18AHK/TU-C18AHK”</t>
+          <t>“ال جي LG مكيف سبليت جيت كول 22,000 وحدة بارد ، تنظيف ذاتي - LA242C0.NK0”</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tornado</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TH-C18AHK</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>1.5</v>
-      </c>
+          <t>LA242C0</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -6268,17 +6280,17 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2399</v>
+        <v>4799</v>
       </c>
       <c r="J95" t="n">
-        <v>2399</v>
+        <v>4799</v>
       </c>
       <c r="K95" t="b">
         <v>0</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%aa%d9%88%d8%b1%d9%86%d9%8a%d8%af%d9%88-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-th-c18ahk-tu-c18ahk/</t>
+          <t>https://alkhaterstore.com/product/%d8%a7%d9%84-%d8%ac%d9%8a-lg-%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-%d8%ac%d9%8a%d8%aa-%d9%83%d9%88%d9%84-22000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%8c-%d8%aa%d9%86/</t>
         </is>
       </c>
       <c r="M95" t="n">
@@ -6293,25 +6305,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AC08598</t>
+          <t>AC07146</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “ال جي LG مكيف سبليت جيت كول 22,000 وحدة بارد ، تنظيف ذاتي - LA242C0.NK0”</t>
+          <t>“مكيف الزامل شباك 1.5 طن 18000 وحدة بارد - ZCM18CGXFMNNW1”</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Zamil</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LA242C0</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>ZCM18CGXFMNNW1</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -6319,7 +6333,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6328,17 +6342,17 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4799</v>
+        <v>1999</v>
       </c>
       <c r="J96" t="n">
-        <v>4799</v>
+        <v>1999</v>
       </c>
       <c r="K96" t="b">
         <v>0</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d8%a7%d9%84-%d8%ac%d9%8a-lg-%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-%d8%ac%d9%8a%d8%aa-%d9%83%d9%88%d9%84-22000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%8c-%d8%aa%d9%86/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84%d8%b2%d8%a7%d9%85%d9%84-%d8%b4%d8%a8%d8%a7%d9%83-1-5-%d8%b7%d9%86-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-zcm18cgxfmnnw1/</t>
         </is>
       </c>
       <c r="M96" t="n">
@@ -6353,26 +6367,26 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AC07146</t>
+          <t>AC08335</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف الزامل شباك 1.5 طن 18000 وحدة بارد - ZCM18CGXFMNNW1”</t>
+          <t>“وستنجهاوس مكيف 27400 وحدة 2.5 طن بارد تبريد توربو، واي فاي - WWS30Z24I/C”</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Zamil</t>
+          <t>Westinghouse</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ZCM18CGXFMNNW1</t>
+          <t>WWS30Z24I</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -6381,7 +6395,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6390,17 +6404,17 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1999</v>
+        <v>4499</v>
       </c>
       <c r="J97" t="n">
-        <v>1999</v>
+        <v>4499</v>
       </c>
       <c r="K97" t="b">
         <v>0</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84%d8%b2%d8%a7%d9%85%d9%84-%d8%b4%d8%a8%d8%a7%d9%83-1-5-%d8%b7%d9%86-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-zcm18cgxfmnnw1/</t>
+          <t>https://alkhaterstore.com/product/wws30z24i-c-%d9%85%d9%83%d9%8a%d9%81-%d9%88%d8%b3%d8%aa%d9%86%d8%ac%d9%87%d8%a7%d9%88%d8%b3-27400-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%aa%d8%a8%d8%b1%d9%8a%d8%af-%d8%aa%d9%88%d8%b1/</t>
         </is>
       </c>
       <c r="M97" t="n">
@@ -6415,26 +6429,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AC08335</t>
+          <t>AC05922</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “وستنجهاوس مكيف 27400 وحدة 2.5 طن بارد تبريد توربو، واي فاي - WWS30Z24I/C”</t>
+          <t>“مكيف ميديا ميشن اكستريم 22100 وحدة بارد جداري - MSTMX24CRNAG1”</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Westinghouse</t>
+          <t>Midea</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>WWS30Z24I</t>
+          <t>MSTMX24CRNAG1</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -6452,17 +6466,17 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4499</v>
+        <v>3254</v>
       </c>
       <c r="J98" t="n">
-        <v>4499</v>
+        <v>3254</v>
       </c>
       <c r="K98" t="b">
         <v>0</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/wws30z24i-c-%d9%85%d9%83%d9%8a%d9%81-%d9%88%d8%b3%d8%aa%d9%86%d8%ac%d9%87%d8%a7%d9%88%d8%b3-27400-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%aa%d8%a8%d8%b1%d9%8a%d8%af-%d8%aa%d9%88%d8%b1/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d9%85%d9%8a%d8%b4%d9%86-%d8%a7%d9%83%d8%b3%d8%aa%d8%b1%d9%8a%d9%85-22100-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7/</t>
         </is>
       </c>
       <c r="M98" t="n">
@@ -6477,26 +6491,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AC05922</t>
+          <t>AC07386</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف ميديا ميشن اكستريم 22100 وحدة بارد جداري - MSTMX24CRNAG1”</t>
+          <t>“ مكيف يونيستار 18500 وحدة بارد جداري UNST 18 SC”</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Midea</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>MSTMX24CRNAG1</t>
-        </is>
-      </c>
+          <t>Unistar</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -6514,17 +6524,17 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3254</v>
+        <v>2199</v>
       </c>
       <c r="J99" t="n">
-        <v>3254</v>
+        <v>2199</v>
       </c>
       <c r="K99" t="b">
         <v>0</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d9%85%d9%8a%d8%b4%d9%86-%d8%a7%d9%83%d8%b3%d8%aa%d8%b1%d9%8a%d9%85-22100-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%8a%d9%88%d9%86%d9%8a%d8%b3%d8%aa%d8%a7%d8%b1-18500-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-unst-18-sc/</t>
         </is>
       </c>
       <c r="M99" t="n">
@@ -6539,18 +6549,26 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AC07386</t>
+          <t>AC07593</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “ مكيف يونيستار 18500 وحدة بارد جداري UNST 18 SC”</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
+          <t>“MP-NF23-30C مكيف ماندو بلس 28000 وحدة بارد واي فاي”</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Mando</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>MP-NF23-30C</t>
+        </is>
+      </c>
       <c r="E100" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -6568,17 +6586,17 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2199</v>
+        <v>4259</v>
       </c>
       <c r="J100" t="n">
-        <v>2199</v>
+        <v>4259</v>
       </c>
       <c r="K100" t="b">
         <v>0</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%8a%d9%88%d9%86%d9%8a%d8%b3%d8%aa%d8%a7%d8%b1-18500-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-unst-18-sc/</t>
+          <t>https://alkhaterstore.com/product/mp-nf23-30c-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d8%a7%d9%86%d8%af%d9%88-%d8%a8%d9%84%d8%b3-28000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
         </is>
       </c>
       <c r="M100" t="n">
@@ -6593,26 +6611,26 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AC07593</t>
+          <t>AC08635</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “MP-NF23-30C مكيف ماندو بلس 28000 وحدة بارد واي فاي”</t>
+          <t>“كرافت مكيف شباك 21800 وحدة , 2 طن , بارد  - CWACH24C”</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Mando</t>
+          <t>Crafft</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>MP-NF23-30C</t>
+          <t>CWACH24C</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -6621,7 +6639,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6630,17 +6648,17 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4259</v>
+        <v>1999</v>
       </c>
       <c r="J101" t="n">
-        <v>4259</v>
+        <v>1999</v>
       </c>
       <c r="K101" t="b">
         <v>0</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/mp-nf23-30c-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d8%a7%d9%86%d8%af%d9%88-%d8%a8%d9%84%d8%b3-28000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
+          <t>https://alkhaterstore.com/product/%d9%83%d8%b1%d8%a7%d9%81%d8%aa-%d9%85%d9%83%d9%8a%d9%81-%d8%b4%d8%a8%d8%a7%d9%83-21800-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-cwach24c/</t>
         </is>
       </c>
       <c r="M101" t="n">
@@ -6655,18 +6673,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AC08635</t>
+          <t>AC07860</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “كرافت مكيف شباك 21800 وحدة , 2 طن , بارد  - CWACH24C”</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>“مكيف جري اي برو 24000 وحدة 2 طن حار بارد انفرتر جداري - GWH24AVEXF-S6DTA1B”</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Gree</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CWACH24C</t>
+          <t>GWH24AVEXF-S6DTA1B</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -6679,7 +6701,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6688,17 +6710,17 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1999</v>
+        <v>5899</v>
       </c>
       <c r="J102" t="n">
-        <v>1999</v>
+        <v>5899</v>
       </c>
       <c r="K102" t="b">
         <v>0</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%83%d8%b1%d8%a7%d9%81%d8%aa-%d9%85%d9%83%d9%8a%d9%81-%d8%b4%d8%a8%d8%a7%d9%83-21800-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-cwach24c/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a7%d9%8a-%d8%a8%d8%b1%d9%88-24000-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%a7%d9%86%d9%81%d8%b1%d8%aa/</t>
         </is>
       </c>
       <c r="M102" t="n">
@@ -6713,26 +6735,26 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AC07860</t>
+          <t>AC08349</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري اي برو 24000 وحدة 2 طن حار بارد انفرتر جداري - GWH24AVEXF-S6DTA1B”</t>
+          <t>“WWS12Z24I/C - مكيف وايت وستنجهاوس 12100 وحدة بارد تبريد توربو، واي فاي”</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Westinghouse</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>GWH24AVEXF-S6DTA1B</t>
+          <t>WWS12Z24I</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -6750,17 +6772,17 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5899</v>
+        <v>1911</v>
       </c>
       <c r="J103" t="n">
-        <v>5899</v>
+        <v>1911</v>
       </c>
       <c r="K103" t="b">
         <v>0</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a7%d9%8a-%d8%a8%d8%b1%d9%88-24000-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%a7%d9%86%d9%81%d8%b1%d8%aa/</t>
+          <t>https://alkhaterstore.com/product/wws12z24i-c/</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -6775,26 +6797,26 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AC08349</t>
+          <t>AC08323</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “WWS12Z24I/C - مكيف وايت وستنجهاوس 12100 وحدة بارد تبريد توربو، واي فاي”</t>
+          <t>“اس كي ام SKM مكيف شباك 17500وحدة حار بارد - WSKMP-18EWTCF0”</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Westinghouse</t>
+          <t>SKM</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>WWS12Z24I</t>
+          <t>WSKMP-18EWTCF0</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -6803,7 +6825,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6812,17 +6834,17 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1911</v>
+        <v>1699</v>
       </c>
       <c r="J104" t="n">
-        <v>1911</v>
+        <v>1699</v>
       </c>
       <c r="K104" t="b">
         <v>0</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/wws12z24i-c/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d8%b3-%d9%83%d9%8a-%d8%a7%d9%85-%d8%b4%d8%a8%d8%a7%d9%83-17500%d9%88%d8%ad%d8%af%d8%a9-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-skm-wskmp-18ewtcf0/</t>
         </is>
       </c>
       <c r="M104" t="n">
@@ -6837,26 +6859,26 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AC08323</t>
+          <t>AC06134</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “اس كي ام SKM مكيف شباك 17500وحدة حار بارد - WSKMP-18EWTCF0”</t>
+          <t>“مكيف هاير سبليت 22000 وحدة بارد واي فاي  HSU-24LPB13/R2(T3)”</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SKM</t>
+          <t>Haier</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>WSKMP-18EWTCF0</t>
+          <t>HSU-24LPB13</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -6865,7 +6887,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6874,17 +6896,17 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1699</v>
+        <v>3179</v>
       </c>
       <c r="J105" t="n">
-        <v>1699</v>
+        <v>3179</v>
       </c>
       <c r="K105" t="b">
         <v>0</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d8%b3-%d9%83%d9%8a-%d8%a7%d9%85-%d8%b4%d8%a8%d8%a7%d9%83-17500%d9%88%d8%ad%d8%af%d8%a9-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-skm-wskmp-18ewtcf0/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%87%d8%a7%d9%8a%d8%b1-22000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%88%d8%a7%d9%8a-%d9%81%d8%a7%d9%8a-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-hsu-24lpb13-r2t3/</t>
         </is>
       </c>
       <c r="M105" t="n">
@@ -6899,26 +6921,26 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AC06134</t>
+          <t>AC07587</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف هاير سبليت 22000 وحدة بارد واي فاي  HSU-24LPB13/R2(T3)”</t>
+          <t>“MP-NF23-12C مكيف ماندو بلس 12100 وحدة بارد جداري”</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Haier</t>
+          <t>Mando</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>HSU-24LPB13</t>
+          <t>MP-NF23-12C</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -6936,17 +6958,17 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3179</v>
+        <v>1899</v>
       </c>
       <c r="J106" t="n">
-        <v>3179</v>
+        <v>1899</v>
       </c>
       <c r="K106" t="b">
         <v>0</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%87%d8%a7%d9%8a%d8%b1-22000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%88%d8%a7%d9%8a-%d9%81%d8%a7%d9%8a-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-hsu-24lpb13-r2t3/</t>
+          <t>https://alkhaterstore.com/product/mp-nf23-12c-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d8%a7%d9%86%d8%af%d9%88-%d8%a8%d9%84%d8%b3-12100-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
         </is>
       </c>
       <c r="M106" t="n">
@@ -6961,26 +6983,26 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AC07587</t>
+          <t>AC06584</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “MP-NF23-12C مكيف ماندو بلس 12100 وحدة بارد جداري”</t>
+          <t>“مكيف جري 22500 وحدة , 2 طن , حار بارد - جداري واي فاي - GWH24AGE-D3NTA1E”</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mando</t>
+          <t>Gree</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>MP-NF23-12C</t>
+          <t>GWH24AGE-D3NTA1E</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6998,17 +7020,17 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1899</v>
+        <v>4199</v>
       </c>
       <c r="J107" t="n">
-        <v>1899</v>
+        <v>4199</v>
       </c>
       <c r="K107" t="b">
         <v>0</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/mp-nf23-12c-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d8%a7%d9%86%d8%af%d9%88-%d8%a8%d9%84%d8%b3-12100-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-23000-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d9%88%d8%a7%d9%8a-%d9%81/</t>
         </is>
       </c>
       <c r="M107" t="n">
@@ -7023,30 +7045,30 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AC06584</t>
+          <t>AC08622</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري 22500 وحدة , 2 طن , حار بارد - جداري واي فاي - GWH24AGE-D3NTA1E”</t>
+          <t>“BSACCA-FI30CB/Bمكيف بيسك 30000 وحدة بارد انفيرتر جداري”</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Basic</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>GWH24AGE-D3NTA1E</t>
+          <t>BSACCA-FI30CB</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rotary</t>
+          <t>Inverter</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7060,17 +7082,17 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4199</v>
+        <v>4699</v>
       </c>
       <c r="J108" t="n">
-        <v>4199</v>
+        <v>4699</v>
       </c>
       <c r="K108" t="b">
         <v>0</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-23000-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d9%88%d8%a7%d9%8a-%d9%81/</t>
+          <t>https://alkhaterstore.com/product/%d8%a8%d9%8a%d8%b3%d9%83-%d9%85%d9%83%d9%8a%d9%81-27400-%d9%88%d8%ad%d8%af%d8%a9-2-5-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-%d8%b3%d8%a8%d9%84%d8%aa-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-bsacca/</t>
         </is>
       </c>
       <c r="M108" t="n">
@@ -7085,26 +7107,30 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AC08622</t>
+          <t>AC07862</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “BSACCA-FI30CB/Bمكيف بيسك 30000 وحدة بارد انفيرتر جداري”</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>“مكيف جري اي برو 34800 وحدة - بارد سبلت انفرتر - GWC36QFXH- S6DTB4A”</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Gree</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>BSACCA-FI30CB</t>
+          <t>GWC36QFXH</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Inverter</t>
+          <t>Rotary</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -7118,21 +7144,21 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4699</v>
+        <v>7699</v>
       </c>
       <c r="J109" t="n">
-        <v>4699</v>
+        <v>7699</v>
       </c>
       <c r="K109" t="b">
         <v>0</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d8%a8%d9%8a%d8%b3%d9%83-%d9%85%d9%83%d9%8a%d9%81-27400-%d9%88%d8%ad%d8%af%d8%a9-2-5-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-%d8%b3%d8%a8%d9%84%d8%aa-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-bsacca/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a7%d9%8a-%d8%a8%d8%b1%d9%88-34800-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%b3%d8%a8%d9%84%d8%aa-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-gw/</t>
         </is>
       </c>
       <c r="M109" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -7143,21 +7169,27 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AC03364</t>
+          <t>AC08353</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “خدمة فك مكيف سبليت - Split air conditioner removal service”</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>“مكيف سبليت هوم كوين 18000 وحدة واي فاي بارد - HQAS180C”</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Home Queen</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>SPLIT</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>HQAS180C</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -7174,17 +7206,17 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>120</v>
+        <v>2516</v>
       </c>
       <c r="J110" t="n">
-        <v>120</v>
+        <v>2516</v>
       </c>
       <c r="K110" t="b">
         <v>0</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/removal-service/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-%d9%87%d9%88%d9%85-%d9%83%d9%88%d9%8a%d9%86-18000-%d9%88%d8%ad%d8%af%d8%a9-%d9%88%d8%a7%d9%8a-%d9%81%d8%a7%d9%8a-%d8%a8%d8%a7%d8%b1%d8%af-hqas/</t>
         </is>
       </c>
       <c r="M110" t="n">
@@ -7199,26 +7231,26 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AC07862</t>
+          <t>AC05394</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري اي برو 34800 وحدة - بارد سبلت انفرتر - GWC36QFXH- S6DTB4A”</t>
+          <t>“MSTE30CRN4AB4 - مكيف ميديا إليت 27200 وحدة بارد جداري”</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Midea</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>GWC36QFXH</t>
+          <t>MSTE30CRN4AB4</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -7236,17 +7268,17 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7699</v>
+        <v>3994</v>
       </c>
       <c r="J111" t="n">
-        <v>7699</v>
+        <v>3994</v>
       </c>
       <c r="K111" t="b">
         <v>0</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a7%d9%8a-%d8%a8%d8%b1%d9%88-34800-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%b3%d8%a8%d9%84%d8%aa-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-gw/</t>
+          <t>https://alkhaterstore.com/product/mste30crn4ab4-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d8%a5%d9%84%d9%8a%d8%aa-27200%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
         </is>
       </c>
       <c r="M111" t="n">
@@ -7261,26 +7293,26 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AC08353</t>
+          <t>AC04981</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف سبليت هوم كوين 18000 وحدة واي فاي بارد - HQAS180C”</t>
+          <t>“مكيف فريجو 21500وحدة بارد جداري - FW24X2H22”</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Home Queen</t>
+          <t>Frigidaire</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>HQAS180C</t>
+          <t>FW24X2H22</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -7298,17 +7330,17 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2516</v>
+        <v>2939</v>
       </c>
       <c r="J112" t="n">
-        <v>2516</v>
+        <v>2939</v>
       </c>
       <c r="K112" t="b">
         <v>0</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-%d9%87%d9%88%d9%85-%d9%83%d9%88%d9%8a%d9%86-18000-%d9%88%d8%ad%d8%af%d8%a9-%d9%88%d8%a7%d9%8a-%d9%81%d8%a7%d9%8a-%d8%a8%d8%a7%d8%b1%d8%af-hqas/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%81%d8%b1%d9%8a%d8%ac%d9%88-21500%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-fw24x2h22/</t>
         </is>
       </c>
       <c r="M112" t="n">
@@ -7323,26 +7355,26 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AC05394</t>
+          <t>AC07472</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “MSTE30CRN4AB4 - مكيف ميديا إليت 27200 وحدة بارد جداري”</t>
+          <t>“ASSA18FUTAZ مكيف جنرال جداري 19600 وحدة ، بارد”</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Midea</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>MSTE30CRN4AB4</t>
+          <t>ASSA18FUTAZ</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -7360,17 +7392,17 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3994</v>
+        <v>4469</v>
       </c>
       <c r="J113" t="n">
-        <v>3994</v>
+        <v>4469</v>
       </c>
       <c r="K113" t="b">
         <v>0</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/mste30crn4ab4-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d8%a5%d9%84%d9%8a%d8%aa-27200%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
+          <t>https://alkhaterstore.com/product/assa18futaz-%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d9%86%d8%b1%d8%a7%d9%84-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-19600-%d9%88%d8%ad%d8%af%d8%a9-%d8%8c-%d8%a8%d8%a7%d8%b1%d8%af/</t>
         </is>
       </c>
       <c r="M113" t="n">
@@ -7385,26 +7417,26 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AC04981</t>
+          <t>AC07822</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف فريجو 21500وحدة بارد جداري - FW24X2H22”</t>
+          <t>“مكيف سبلت يوركس 21000 وحدة بارد - YORX-24KC”</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Frigidaire</t>
+          <t>Yorksa</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>FW24X2H22</t>
+          <t>YORX-24KC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -7422,17 +7454,17 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2939</v>
+        <v>2749</v>
       </c>
       <c r="J114" t="n">
-        <v>2939</v>
+        <v>2749</v>
       </c>
       <c r="K114" t="b">
         <v>0</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%81%d8%b1%d9%8a%d8%ac%d9%88-21500%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-fw24x2h22/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d8%aa-%d9%8a%d9%88%d8%b1%d9%83%d8%b3-21000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-yorx-24kc/</t>
         </is>
       </c>
       <c r="M114" t="n">
@@ -7447,22 +7479,26 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AC07472</t>
+          <t>AC07853</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “ASSA18FUTAZ مكيف جنرال جداري 19600 وحدة ، بارد”</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
+          <t>“مكيف جري اي برو 30000 وحدة 2.5 طن بارد انفرتر واي فاي - GWC30AVEXH-S6DTA1B”</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Gree</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ASSA18FUTAZ</t>
+          <t>GWC30AVEXH-S6DTA1B</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -7480,17 +7516,17 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4469</v>
+        <v>7049</v>
       </c>
       <c r="J115" t="n">
-        <v>4469</v>
+        <v>7049</v>
       </c>
       <c r="K115" t="b">
         <v>0</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/assa18futaz-%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d9%86%d8%b1%d8%a7%d9%84-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-19600-%d9%88%d8%ad%d8%af%d8%a9-%d8%8c-%d8%a8%d8%a7%d8%b1%d8%af/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a7%d9%8a-%d8%a8%d8%b1%d9%88-30000-%d9%88%d8%ad%d8%af%d8%a9-2-5-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d9%88%d8%a7/</t>
         </is>
       </c>
       <c r="M115" t="n">
@@ -7505,18 +7541,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AC07822</t>
+          <t>AC07851</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف سبلت يوركس 21000 وحدة بارد - YORX-24KC”</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>“مكيف جري اي برو 18000 وحدة 1.5 طن سبلت بارد انفرتر واي فاي - GWC18AVDXF-S6DTA1C”</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Gree</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>YORX-24KC</t>
+          <t>GWC18AVDXF-S6DTA1C</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -7538,17 +7578,17 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2749</v>
+        <v>4715</v>
       </c>
       <c r="J116" t="n">
-        <v>2749</v>
+        <v>4715</v>
       </c>
       <c r="K116" t="b">
         <v>0</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d8%aa-%d9%8a%d9%88%d8%b1%d9%83%d8%b3-21000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-yorx-24kc/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a7%d9%8a-%d8%a8%d8%b1%d9%88-18000-%d9%88%d8%ad%d8%af%d8%a9-1-5-%d8%b7%d9%86-%d8%b3%d8%a8%d9%84%d8%aa-%d8%a8%d8%a7%d8%b1%d8%af-%d8%a7%d9%86%d9%81%d8%b1/</t>
         </is>
       </c>
       <c r="M116" t="n">
@@ -7563,27 +7603,25 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AC07853</t>
+          <t>AC08053</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري اي برو 30000 وحدة 2.5 طن بارد انفرتر واي فاي - GWC30AVEXH-S6DTA1B”</t>
+          <t>“مكيف دانسات 11100 وحده فلتر نانو ضد البكتريا بارد - DSA12C”</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Dansat</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>GWC30AVEXH-S6DTA1B</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>2.5</v>
-      </c>
+          <t>DSA12C</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -7600,17 +7638,17 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>7049</v>
+        <v>1799</v>
       </c>
       <c r="J117" t="n">
-        <v>7049</v>
+        <v>1799</v>
       </c>
       <c r="K117" t="b">
         <v>0</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a7%d9%8a-%d8%a8%d8%b1%d9%88-30000-%d9%88%d8%ad%d8%af%d8%a9-2-5-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d9%88%d8%a7/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%af%d8%a7%d9%86%d8%b3%d8%a7%d8%aa-11100-%d9%88%d8%ad%d8%af%d9%87-%d9%81%d9%84%d8%aa%d8%b1-%d9%86%d8%a7%d9%86%d9%88-%d8%b6%d8%af-%d8%a7%d9%84%d8%a8%d9%83%d8%aa%d8%b1%d9%8a/</t>
         </is>
       </c>
       <c r="M117" t="n">
@@ -7625,22 +7663,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AC07851</t>
+          <t>AC06330</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري اي برو 18000 وحدة 1.5 طن سبلت بارد انفرتر واي فاي - GWC18AVDXF-S6DTA1C”</t>
+          <t>“سوبر جينرال مكيف سبليت 21000 وحدة، اونو، ريش ذهبية، بارد - KSGS243GE”</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Super General</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>GWC18AVDXF-S6DTA1C</t>
+          <t>KSGS243GE</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -7662,17 +7700,17 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4715</v>
+        <v>4299</v>
       </c>
       <c r="J118" t="n">
-        <v>4715</v>
+        <v>4299</v>
       </c>
       <c r="K118" t="b">
         <v>0</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a7%d9%8a-%d8%a8%d8%b1%d9%88-18000-%d9%88%d8%ad%d8%af%d8%a9-1-5-%d8%b7%d9%86-%d8%b3%d8%a8%d9%84%d8%aa-%d8%a8%d8%a7%d8%b1%d8%af-%d8%a7%d9%86%d9%81%d8%b1/</t>
+          <t>https://alkhaterstore.com/product/%d8%b3%d9%88%d8%a8%d8%b1-%d8%ac%d9%8a%d9%86%d8%b1%d8%a7%d9%84-%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-21000-%d9%88%d8%ad%d8%af%d8%a9%d8%8c-%d8%a7%d9%88%d9%86%d9%88%d8%8c-%d8%b1%d9%8a/</t>
         </is>
       </c>
       <c r="M118" t="n">
@@ -7687,22 +7725,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AC08053</t>
+          <t>AC08369</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف دانسات 11100 وحده فلتر نانو ضد البكتريا بارد - DSA12C”</t>
+          <t>“فريجو مكيف سبليت  12600 الف وحدة جالاكسي بلس حار بارد - FW12X2P22”</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dansat</t>
+          <t>Frigidaire</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DSA12C</t>
+          <t>FW12X2P22</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -7722,17 +7760,17 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1799</v>
+        <v>2100</v>
       </c>
       <c r="J119" t="n">
-        <v>1799</v>
+        <v>2100</v>
       </c>
       <c r="K119" t="b">
         <v>0</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%af%d8%a7%d9%86%d8%b3%d8%a7%d8%aa-11100-%d9%88%d8%ad%d8%af%d9%87-%d9%81%d9%84%d8%aa%d8%b1-%d9%86%d8%a7%d9%86%d9%88-%d8%b6%d8%af-%d8%a7%d9%84%d8%a8%d9%83%d8%aa%d8%b1%d9%8a/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa%d8%8c%d9%81%d8%b1%d9%8a%d8%ac%d9%88-%d8%8c-12600-%d8%a7%d9%84%d9%81-%d9%88%d8%ad%d8%af%d8%a9-%d8%ac%d8%a7%d9%84%d8%a7%d9%83%d8%b3%d9%8a-%d8%a8/</t>
         </is>
       </c>
       <c r="M119" t="n">
@@ -7747,22 +7785,26 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AC06330</t>
+          <t>AC06768</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “سوبر جينرال مكيف سبليت 21000 وحدة، اونو، ريش ذهبية، بارد - KSGS243GE”</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
+          <t>“إل جي مكيف سبليت - 22800 وحدة - بارد - LO242C0.NK”</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>KSGS243GE</t>
+          <t>LO242C0</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -7780,17 +7822,17 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4299</v>
+        <v>3299</v>
       </c>
       <c r="J120" t="n">
-        <v>4299</v>
+        <v>3299</v>
       </c>
       <c r="K120" t="b">
         <v>0</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d8%b3%d9%88%d8%a8%d8%b1-%d8%ac%d9%8a%d9%86%d8%b1%d8%a7%d9%84-%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-21000-%d9%88%d8%ad%d8%af%d8%a9%d8%8c-%d8%a7%d9%88%d9%86%d9%88%d8%8c-%d8%b1%d9%8a/</t>
+          <t>https://alkhaterstore.com/product/%d8%a5%d9%84-%d8%ac%d9%8a-%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-22800-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%81%d9%82%d8%b7-%d8%a3%d8%a8%d9%8a%d8%b6/</t>
         </is>
       </c>
       <c r="M120" t="n">
@@ -7805,25 +7847,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AC08369</t>
+          <t>AC07583</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “فريجو مكيف سبليت  12600 الف وحدة جالاكسي بلس حار بارد - FW12X2P22”</t>
+          <t>“مكيف ماندو شباك 18000 وحدة بارد - W21-18C”</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Frigidaire</t>
+          <t>Mando</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>FW12X2P22</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>W21-18C</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -7831,7 +7875,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7840,17 +7884,17 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2100</v>
+        <v>1679</v>
       </c>
       <c r="J121" t="n">
-        <v>2100</v>
+        <v>1679</v>
       </c>
       <c r="K121" t="b">
         <v>0</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa%d8%8c%d9%81%d8%b1%d9%8a%d8%ac%d9%88-%d8%8c-12600-%d8%a7%d9%84%d9%81-%d9%88%d8%ad%d8%af%d8%a9-%d8%ac%d8%a7%d9%84%d8%a7%d9%83%d8%b3%d9%8a-%d8%a8/</t>
+          <t>https://alkhaterstore.com/product/w21-18c-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d8%a7%d9%86%d8%af%d9%88-%d8%b4%d8%a8%d8%a7%d9%83-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af/</t>
         </is>
       </c>
       <c r="M121" t="n">
@@ -7865,17 +7909,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AC06346</t>
+          <t>AC06183</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مبرد هواء سيمفوني 50 لتر مع جهاز تحكم عن بعد بتقنية أي-بيور | DIET 50 i”</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
+          <t>“MPPH12CRN مكيف ميديا متنقل 12000 وحدة بارد”</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Midea</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>MPPH12CRN</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>1</v>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -7892,17 +7946,17 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>959</v>
+        <v>2159</v>
       </c>
       <c r="J122" t="n">
-        <v>959</v>
+        <v>2159</v>
       </c>
       <c r="K122" t="b">
         <v>0</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d8%b3%d9%8a%d9%85%d9%81%d9%88%d9%86%d9%8a-%d9%85%d8%a8%d8%b1%d8%af-%d8%a7%d9%84%d9%87%d9%88%d8%a7%d8%a1-%d8%a7%d9%84%d8%b0%d9%83%d9%8a-%d8%af%d8%a7%d9%8a%d8%aa-50i-%d8%b3%d8%b9%d8%a9-50-%d9%84%d9%8a/</t>
+          <t>https://alkhaterstore.com/product/mpph12crn-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d9%85%d8%aa%d9%86%d9%82%d9%84-12000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af/</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -7917,26 +7971,26 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AC06768</t>
+          <t>AC08819</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “إل جي مكيف سبليت - 22800 وحدة - بارد - LO242C0.NK”</t>
+          <t>“مكيف جري بلس 34200 وحدة , 3 طن , انفرتر - حار , بارد - جداري - GWH36AWFXH-S6DTA1A”</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Gree</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LO242C0</t>
+          <t>GWH36AWFXH-S6DTA1A</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -7954,17 +8008,17 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3299</v>
+        <v>6249</v>
       </c>
       <c r="J123" t="n">
-        <v>3299</v>
+        <v>6249</v>
       </c>
       <c r="K123" t="b">
         <v>0</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d8%a5%d9%84-%d8%ac%d9%8a-%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-22800-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%81%d9%82%d8%b7-%d8%a3%d8%a8%d9%8a%d8%b6/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-34200-%d9%88%d8%ad%d8%af%d8%a9-3-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af/</t>
         </is>
       </c>
       <c r="M123" t="n">
@@ -7979,26 +8033,26 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AC07583</t>
+          <t>AC08814</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف ماندو شباك 18000 وحدة بارد - W21-18C”</t>
+          <t>“مكيف جري بلس 34200 وحدة 3 طن - انفرتر - بارد - جداري - GWC36AWFXH-S6DTA1A”</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Mando</t>
+          <t>Gree</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>W21-18C</t>
+          <t>GWC36AWFXH-S6DTA1A</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -8007,7 +8061,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8016,17 +8070,17 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1679</v>
+        <v>5999</v>
       </c>
       <c r="J124" t="n">
-        <v>1679</v>
+        <v>5999</v>
       </c>
       <c r="K124" t="b">
         <v>0</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/w21-18c-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d8%a7%d9%86%d8%af%d9%88-%d8%b4%d8%a8%d8%a7%d9%83-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-34200-%d9%88%d8%ad%d8%af%d8%a9-3-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7/</t>
         </is>
       </c>
       <c r="M124" t="n">
@@ -8041,26 +8095,26 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AC06183</t>
+          <t>AC08818</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “MPPH12CRN مكيف ميديا متنقل 12000 وحدة بارد”</t>
+          <t>“مكيف جري بلس 30000 وحدة 2.5 طن - انفرتر - حار , بارد - جداري - GWH30AVEXH-S6DTA1A”</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Midea</t>
+          <t>Gree</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>MPPH12CRN</t>
+          <t>GWH30AVEXH-S6DTA1A</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -8078,17 +8132,17 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2159</v>
+        <v>6149</v>
       </c>
       <c r="J125" t="n">
-        <v>2159</v>
+        <v>6149</v>
       </c>
       <c r="K125" t="b">
         <v>0</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/mpph12crn-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d9%85%d8%aa%d9%86%d9%82%d9%84-12000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-30000-%d9%88%d8%ad%d8%af%d8%a9-2-5-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af/</t>
         </is>
       </c>
       <c r="M125" t="n">
@@ -8103,12 +8157,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AC08819</t>
+          <t>AC08817</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري بلس 34200 وحدة , 3 طن , انفرتر - حار , بارد - جداري - GWH36AWFXH-S6DTA1A”</t>
+          <t>“مكيف جري بلس 24000 وحدة , 2 طن - انفرتر - حار , بارد - جداري - GWH24AVEXF-S6DTA1A”</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8118,11 +8172,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>GWH36AWFXH-S6DTA1A</t>
+          <t>GWH24AVEXF-S6DTA1A</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -8140,17 +8194,17 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6249</v>
+        <v>4139</v>
       </c>
       <c r="J126" t="n">
-        <v>6249</v>
+        <v>4139</v>
       </c>
       <c r="K126" t="b">
         <v>0</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-34200-%d9%88%d8%ad%d8%af%d8%a9-3-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-24000-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af/</t>
         </is>
       </c>
       <c r="M126" t="n">
@@ -8165,12 +8219,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AC08814</t>
+          <t>AC08812</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري بلس 34200 وحدة 3 طن - انفرتر - بارد - جداري - GWC36AWFXH-S6DTA1A”</t>
+          <t>“مكيف جري بلس 24000 وحدة , 2 طن - بارد - انفرتر - جداري - GWC24AVEXF-S6DTA1A”</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8180,11 +8234,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>GWC36AWFXH-S6DTA1A</t>
+          <t>GWC24AVEXF-S6DTA1A</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -8202,17 +8256,17 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5999</v>
+        <v>4329</v>
       </c>
       <c r="J127" t="n">
-        <v>5999</v>
+        <v>4329</v>
       </c>
       <c r="K127" t="b">
         <v>0</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-34200-%d9%88%d8%ad%d8%af%d8%a9-3-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-24000-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%ac%d8%af%d8%a7/</t>
         </is>
       </c>
       <c r="M127" t="n">
@@ -8227,12 +8281,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AC08818</t>
+          <t>AC08816</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري بلس 30000 وحدة 2.5 طن - انفرتر - حار , بارد - جداري - GWH30AVEXH-S6DTA1A”</t>
+          <t>“مكيف جري بلس 18000وحدة , 1.5 طن - انفرتر - حار , بارد - جداري - GWH18AVDXE-S6DTA1A”</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8242,11 +8296,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>GWH30AVEXH-S6DTA1A</t>
+          <t>GWH18AVDXE-S6DTA1A</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -8264,17 +8318,17 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6149</v>
+        <v>3392</v>
       </c>
       <c r="J128" t="n">
-        <v>6149</v>
+        <v>3392</v>
       </c>
       <c r="K128" t="b">
         <v>0</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-30000-%d9%88%d8%ad%d8%af%d8%a9-2-5-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-18000%d9%88%d8%ad%d8%af%d8%a9-1-5-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af/</t>
         </is>
       </c>
       <c r="M128" t="n">
@@ -8289,12 +8343,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AC08817</t>
+          <t>AC08811</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري بلس 24000 وحدة , 2 طن - انفرتر - حار , بارد - جداري - GWH24AVEXF-S6DTA1A”</t>
+          <t>“مكيف جري بلس 18000 وحدة 1.5 طن - انفرتر - بارد - جداري - GWC18AVDXE-S6DTA1A”</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8304,11 +8358,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>GWH24AVEXF-S6DTA1A</t>
+          <t>GWC18AVDXE-S6DTA1A</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -8326,17 +8380,17 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4139</v>
+        <v>3099</v>
       </c>
       <c r="J129" t="n">
-        <v>4139</v>
+        <v>3099</v>
       </c>
       <c r="K129" t="b">
         <v>0</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-24000-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-18000-%d9%88%d8%ad%d8%af%d8%a9-1-5-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7/</t>
         </is>
       </c>
       <c r="M129" t="n">
@@ -8351,12 +8405,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AC08812</t>
+          <t>AC08815</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري بلس 24000 وحدة , 2 طن - بارد - انفرتر - جداري - GWC24AVEXF-S6DTA1A”</t>
+          <t>“مكيف جري بلس 12000وحدة 1 طن - حار , بارد - انفرتر - جداري - GWH12AVCXB-S6DTA1A”</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8366,11 +8420,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>GWC24AVEXF-S6DTA1A</t>
+          <t>GWH12AVCXB-S6DTA1A</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -8388,17 +8442,17 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4329</v>
+        <v>2745</v>
       </c>
       <c r="J130" t="n">
-        <v>4329</v>
+        <v>2745</v>
       </c>
       <c r="K130" t="b">
         <v>0</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-24000-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%ac%d8%af%d8%a7/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-12000%d9%88%d8%ad%d8%af%d8%a9-1-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1/</t>
         </is>
       </c>
       <c r="M130" t="n">
@@ -8413,12 +8467,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AC08816</t>
+          <t>AC08809</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري بلس 18000وحدة , 1.5 طن - انفرتر - حار , بارد - جداري - GWH18AVDXE-S6DTA1A”</t>
+          <t>“مكيف جري ماكس 33000 وحدة , 3 طن - حار بارد - جداري - GWH36AWFXH-D6NTA1A”</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8428,11 +8482,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>GWH18AVDXE-S6DTA1A</t>
+          <t>GWH36AWFXH-D6NTA1A</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -8450,21 +8504,21 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3392</v>
+        <v>7349</v>
       </c>
       <c r="J131" t="n">
-        <v>3392</v>
+        <v>7349</v>
       </c>
       <c r="K131" t="b">
         <v>0</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-18000%d9%88%d8%ad%d8%af%d8%a9-1-5-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d9%85%d8%a7%d9%83%d8%b3-33000-%d9%88%d8%ad%d8%af%d8%a9-3-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-gw/</t>
         </is>
       </c>
       <c r="M131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -8475,12 +8529,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AC08811</t>
+          <t>AC08808</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري بلس 18000 وحدة 1.5 طن - انفرتر - بارد - جداري - GWC18AVDXE-S6DTA1A”</t>
+          <t>“مكيف جري ماكس 30000 وحدة 2.5 طن - حار , بارد - جداري - GWH30AVEXH-D6NTA1A”</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8490,11 +8544,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>GWC18AVDXE-S6DTA1A</t>
+          <t>GWH30AVEXH-D6NTA1A</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -8512,21 +8566,21 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3099</v>
+        <v>6149</v>
       </c>
       <c r="J132" t="n">
-        <v>3099</v>
+        <v>6149</v>
       </c>
       <c r="K132" t="b">
         <v>0</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-18000-%d9%88%d8%ad%d8%af%d8%a9-1-5-%d8%b7%d9%86-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d9%85%d8%a7%d9%83%d8%b3-30000-%d9%88%d8%ad%d8%af%d8%a9-2-5-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
         </is>
       </c>
       <c r="M132" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -8537,12 +8591,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AC08815</t>
+          <t>AC08807</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري بلس 12000وحدة 1 طن - حار , بارد - انفرتر - جداري - GWH12AVCXB-S6DTA1A”</t>
+          <t>“مكيف جري ماكس 23200 وحدة 2 طن - حار , بارد - جداري - GWH24AVEXF-D6NTA1A”</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8552,11 +8606,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>GWH12AVCXB-S6DTA1A</t>
+          <t>GWH24AVEXF-D6NTA1A</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -8574,21 +8628,21 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2745</v>
+        <v>3799</v>
       </c>
       <c r="J133" t="n">
-        <v>2745</v>
+        <v>3799</v>
       </c>
       <c r="K133" t="b">
         <v>0</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%84%d8%b3-12000%d9%88%d8%ad%d8%af%d8%a9-1-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d9%85%d8%a7%d9%83%d8%b3-23200-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-gw/</t>
         </is>
       </c>
       <c r="M133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -8599,12 +8653,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AC08809</t>
+          <t>AC08806</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري ماكس 33000 وحدة , 3 طن - حار بارد - جداري - GWH36AWFXH-D6NTA1A”</t>
+          <t>“مكيف جري ماكس 19300 وحدة - حار , بارد - جداري - GWH18AVDXF-D6NTA1A”</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8614,11 +8668,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>GWH36AWFXH-D6NTA1A</t>
+          <t>GWH18AVDXF-D6NTA1A</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -8636,17 +8690,17 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7349</v>
+        <v>3399</v>
       </c>
       <c r="J134" t="n">
-        <v>7349</v>
+        <v>3399</v>
       </c>
       <c r="K134" t="b">
         <v>0</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d9%85%d8%a7%d9%83%d8%b3-33000-%d9%88%d8%ad%d8%af%d8%a9-3-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-gw/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d9%85%d8%a7%d9%83%d8%b3-19300-%d9%88%d8%ad%d8%af%d8%a9-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-gwh18avdxf-d6nta1/</t>
         </is>
       </c>
       <c r="M134" t="n">
@@ -8661,12 +8715,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AC08808</t>
+          <t>AC08805</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري ماكس 30000 وحدة 2.5 طن - حار , بارد - جداري - GWH30AVEXH-D6NTA1A”</t>
+          <t>“مكيف جري ماكس 12200 وحدة - بارد - جداري - GWH12AVCXD-D6NTA1A”</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8676,11 +8730,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>GWH30AVEXH-D6NTA1A</t>
+          <t>GWH12AVCXD-D6NTA1A</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -8698,17 +8752,17 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6149</v>
+        <v>2549</v>
       </c>
       <c r="J135" t="n">
-        <v>6149</v>
+        <v>2549</v>
       </c>
       <c r="K135" t="b">
         <v>0</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d9%85%d8%a7%d9%83%d8%b3-30000-%d9%88%d8%ad%d8%af%d8%a9-2-5-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d9%85%d8%a7%d9%83%d8%b3-12200-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-gwh12avcxd-d6nta1a/</t>
         </is>
       </c>
       <c r="M135" t="n">
@@ -8723,26 +8777,26 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AC08807</t>
+          <t>AC08625</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري ماكس 23200 وحدة 2 طن - حار , بارد - جداري - GWH24AVEXF-D6NTA1A”</t>
+          <t>“مكيف اس كي ام طن , 12000 وحدة جداري - بارد - MSKMP-12CWTCD0”</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Midea</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>GWH24AVEXF-D6NTA1A</t>
+          <t>MSKMP-12CWTCD0</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -8760,17 +8814,17 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3799</v>
+        <v>1799</v>
       </c>
       <c r="J136" t="n">
-        <v>3799</v>
+        <v>1799</v>
       </c>
       <c r="K136" t="b">
         <v>0</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d9%85%d8%a7%d9%83%d8%b3-23200-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-gw/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d8%b3-%d9%83%d9%8a-%d8%a7%d9%85-%d8%b7%d9%86-12000-%d9%88%d8%ad%d8%af%d8%a9-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d8%a8%d8%a7%d8%b1%d8%af-mskmp-12cwtcd0/</t>
         </is>
       </c>
       <c r="M136" t="n">
@@ -8785,26 +8839,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>AC08806</t>
+          <t>AC08414</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري ماكس 19300 وحدة - حار , بارد - جداري - GWH18AVDXF-D6NTA1A”</t>
+          <t>“مكيف ميديا 12100 وحدة ايليت , 1 طن , بارد , جداري - MSTE12CRN1AG2”</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Midea</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>GWH18AVDXF-D6NTA1A</t>
+          <t>MSTE12CRN1AG2</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -8822,17 +8876,17 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3399</v>
+        <v>2149</v>
       </c>
       <c r="J137" t="n">
-        <v>3399</v>
+        <v>2149</v>
       </c>
       <c r="K137" t="b">
         <v>0</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d9%85%d8%a7%d9%83%d8%b3-19300-%d9%88%d8%ad%d8%af%d8%a9-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-gwh18avdxf-d6nta1/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-12100-%d9%88%d8%ad%d8%af%d8%a9-%d8%a7%d9%8a%d9%84%d9%8a%d8%aa-1-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-mst/</t>
         </is>
       </c>
       <c r="M137" t="n">
@@ -8847,26 +8901,26 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AC08805</t>
+          <t>AC07868</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري ماكس 12200 وحدة - بارد - جداري - GWH12AVCXD-D6NTA1A”</t>
+          <t>“مكيف امبكس 21000 وحدة , 2 طن , حار - بارد , جداري - IM24S3MHSA”</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Impax</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>GWH12AVCXD-D6NTA1A</t>
+          <t>IM24S3MHSA</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -8884,17 +8938,17 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2549</v>
+        <v>2599</v>
       </c>
       <c r="J138" t="n">
-        <v>2549</v>
+        <v>2599</v>
       </c>
       <c r="K138" t="b">
         <v>0</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d9%85%d8%a7%d9%83%d8%b3-12200-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-gwh12avcxd-d6nta1a/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%85%d8%a8%d9%83%d8%b3-21000-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-im24s3mhsa/</t>
         </is>
       </c>
       <c r="M138" t="n">
@@ -8909,26 +8963,26 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AC08625</t>
+          <t>AC06894</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف اس كي ام طن , 12000 وحدة جداري - بارد - MSKMP-12CWTCD0”</t>
+          <t>“مكيف جري 18000 وحدة 1.5 طن , واي فاي , حار بارد جداري - GWH18AGD-D3NTA1A”</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Midea</t>
+          <t>Gree</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>MSKMP-12CWTCD0</t>
+          <t>GWH18AGD-D3NTA1A</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -8946,17 +9000,17 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1799</v>
+        <v>3149</v>
       </c>
       <c r="J139" t="n">
-        <v>1799</v>
+        <v>3149</v>
       </c>
       <c r="K139" t="b">
         <v>0</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d8%b3-%d9%83%d9%8a-%d8%a7%d9%85-%d8%b7%d9%86-12000-%d9%88%d8%ad%d8%af%d8%a9-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d8%a8%d8%a7%d8%b1%d8%af-mskmp-12cwtcd0/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-18000-%d9%88%d8%ad%d8%af%d8%a9-1-5-%d8%b7%d9%86-%d9%88%d8%a7%d9%8a-%d9%81%d8%a7%d9%8a-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7/</t>
         </is>
       </c>
       <c r="M139" t="n">
@@ -8971,26 +9025,26 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AC08414</t>
+          <t>AC05822</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف ميديا 12100 وحدة ايليت , 1 طن , بارد , جداري - MSTE12CRN1AG2”</t>
+          <t>“مكيف جري 31800 وحدة 3 طن حار بارد جداري واي فاي - GWH36QF-D3NTB4G”</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Midea</t>
+          <t>Gree</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>MSTE12CRN1AG2</t>
+          <t>GWH36QF-D3NTB4G</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -9008,17 +9062,17 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2149</v>
+        <v>7499</v>
       </c>
       <c r="J140" t="n">
-        <v>2149</v>
+        <v>7499</v>
       </c>
       <c r="K140" t="b">
         <v>0</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-12100-%d9%88%d8%ad%d8%af%d8%a9-%d8%a7%d9%8a%d9%84%d9%8a%d8%aa-1-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-mst/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-31800-%d9%88%d8%ad%d8%af%d8%a9-3-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d9%88%d8%a7%d9%8a-%d9%81%d8%a7/</t>
         </is>
       </c>
       <c r="M140" t="n">
@@ -9033,22 +9087,26 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>AC07868</t>
+          <t>AC08623</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف امبكس 21000 وحدة , 2 طن , حار - بارد , جداري - IM24S3MHSA”</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
+          <t>“بيسك مكيف 31400 وحدة , 3 طن بارد - سبلت - انفرتر - BSACCA-FI36CB/B”</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>IM24S3MHSA</t>
+          <t>BSACCA-FI36CB</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -9066,17 +9124,17 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2599</v>
+        <v>4999</v>
       </c>
       <c r="J141" t="n">
-        <v>2599</v>
+        <v>4999</v>
       </c>
       <c r="K141" t="b">
         <v>0</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%85%d8%a8%d9%83%d8%b3-21000-%d9%88%d8%ad%d8%af%d8%a9-2-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-im24s3mhsa/</t>
+          <t>https://alkhaterstore.com/product/%d8%a8%d9%8a%d8%b3%d9%83-%d9%85%d9%83%d9%8a%d9%81-31400-%d9%88%d8%ad%d8%af%d8%a9-3-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-%d8%b3%d8%a8%d9%84%d8%aa-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-bsacca-fi/</t>
         </is>
       </c>
       <c r="M141" t="n">
@@ -9091,12 +9149,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>AC06894</t>
+          <t>AC06843</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري 18000 وحدة 1.5 طن , واي فاي , حار بارد جداري - GWH18AGD-D3NTA1A”</t>
+          <t>“مكيف جري بولر برو 18000 وحدة 1.5 طن سبلت حار / بارد انفرتر واي فاي - GWH18AGD-S3DTA1A”</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9106,7 +9164,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>GWH18AGD-D3NTA1A</t>
+          <t>GWH18AGD-S3DTA1A</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -9128,17 +9186,17 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3149</v>
+        <v>4199</v>
       </c>
       <c r="J142" t="n">
-        <v>3149</v>
+        <v>4199</v>
       </c>
       <c r="K142" t="b">
         <v>0</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-18000-%d9%88%d8%ad%d8%af%d8%a9-1-5-%d8%b7%d9%86-%d9%88%d8%a7%d9%8a-%d9%81%d8%a7%d9%8a-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%88%d9%84%d8%b1-%d8%a8%d8%b1%d9%88-18000-%d9%88%d8%ad%d8%af%d8%a9-1-5-%d8%b7%d9%86-%d8%b3%d8%a8%d9%84%d8%aa-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1/</t>
         </is>
       </c>
       <c r="M142" t="n">
@@ -9153,26 +9211,26 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>AC05822</t>
+          <t>AC08589</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري 31800 وحدة 3 طن حار بارد جداري واي فاي - GWH36QF-D3NTB4G”</t>
+          <t>“تي سي ال TCL مكيف متنقل 14000 وحدة بارد - TAC-14CPA/DM”</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>TCL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>GWH36QF-D3NTB4G</t>
+          <t>TAC-14CPA</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -9190,17 +9248,17 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>7499</v>
+        <v>2199</v>
       </c>
       <c r="J143" t="n">
-        <v>7499</v>
+        <v>2199</v>
       </c>
       <c r="K143" t="b">
         <v>0</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-31800-%d9%88%d8%ad%d8%af%d8%a9-3-%d8%b7%d9%86-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d9%88%d8%a7%d9%8a-%d9%81%d8%a7/</t>
+          <t>https://alkhaterstore.com/product/%d8%aa%d9%8a-%d8%b3%d9%8a-%d8%a7%d9%84-tcl-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d8%aa%d9%86%d9%82%d9%84-14000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-tac-14cpa-dm/</t>
         </is>
       </c>
       <c r="M143" t="n">
@@ -9215,22 +9273,26 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AC08623</t>
+          <t>AC05906</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “بيسك مكيف 31400 وحدة , 3 طن بارد - سبلت - انفرتر - BSACCA-FI36CB/B”</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
+          <t>“مكيف جري 21800 وحدة بارد شباك - GJC24AE-D3NMTD5D”</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>BSACCA-FI36CB</t>
+          <t>GJC24AE-D3NMTD5D</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -9239,7 +9301,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9248,17 +9310,17 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4999</v>
+        <v>2480</v>
       </c>
       <c r="J144" t="n">
-        <v>4999</v>
+        <v>2480</v>
       </c>
       <c r="K144" t="b">
         <v>0</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d8%a8%d9%8a%d8%b3%d9%83-%d9%85%d9%83%d9%8a%d9%81-31400-%d9%88%d8%ad%d8%af%d8%a9-3-%d8%b7%d9%86-%d8%a8%d8%a7%d8%b1%d8%af-%d8%b3%d8%a8%d9%84%d8%aa-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-bsacca-fi/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-21800-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%b4%d8%a8%d8%a7%d9%83-gjc24ae-d3nmtd5d/</t>
         </is>
       </c>
       <c r="M144" t="n">
@@ -9273,22 +9335,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AC06843</t>
+          <t>AC07867</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري بولر برو 18000 وحدة 1.5 طن سبلت حار / بارد انفرتر واي فاي - GWH18AGD-S3DTA1A”</t>
+          <t>“مكيف امبيكس سبلت 21000 وحدة بارد-IM24S3CCSA FAN”</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Impax</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>GWH18AGD-S3DTA1A</t>
+          <t>IM24S3CCSA</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -9310,17 +9372,17 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4199</v>
+        <v>2749</v>
       </c>
       <c r="J145" t="n">
-        <v>4199</v>
+        <v>2749</v>
       </c>
       <c r="K145" t="b">
         <v>0</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%a8%d9%88%d9%84%d8%b1-%d8%a8%d8%b1%d9%88-18000-%d9%88%d8%ad%d8%af%d8%a9-1-5-%d8%b7%d9%86-%d8%b3%d8%a8%d9%84%d8%aa-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%85%d8%a8%d9%8a%d9%83%d8%b3-%d8%b3%d8%a8%d9%84%d8%aa-21000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-im24s3ccsa-fan/</t>
         </is>
       </c>
       <c r="M145" t="n">
@@ -9335,26 +9397,26 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AC08589</t>
+          <t>AC08327</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “تي سي ال TCL مكيف متنقل 14000 وحدة بارد - TAC-14CPA/DM”</t>
+          <t>“هاير مكيف سبليت 27400 وحده 2.5 طن نانو واي فاي بارد - HSU-30LPC13/R2(T3)”</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TCL</t>
+          <t>Haier</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>TAC-14CPA</t>
+          <t>HSU-30LPC13</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -9372,17 +9434,17 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2199</v>
+        <v>4999</v>
       </c>
       <c r="J146" t="n">
-        <v>2199</v>
+        <v>4999</v>
       </c>
       <c r="K146" t="b">
         <v>0</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d8%aa%d9%8a-%d8%b3%d9%8a-%d8%a7%d9%84-tcl-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d8%aa%d9%86%d9%82%d9%84-14000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-tac-14cpa-dm/</t>
+          <t>https://alkhaterstore.com/product/hsu-30lpc13-r2t3/</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -9397,22 +9459,22 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>AC05906</t>
+          <t>AC08262</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري 21800 وحدة بارد شباك - GJC24AE-D3NMTD5D”</t>
+          <t>“MSTN24CRNAG16 - مكيف ميديا انفينتي 22000 وحدة بارد جداري اسود”</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Midea</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>GJC24AE-D3NMTD5D</t>
+          <t>MSTN24CRNAG16</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -9425,7 +9487,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9434,17 +9496,17 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2480</v>
+        <v>3999</v>
       </c>
       <c r="J147" t="n">
-        <v>2480</v>
+        <v>3999</v>
       </c>
       <c r="K147" t="b">
         <v>0</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-21800-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%b4%d8%a8%d8%a7%d9%83-gjc24ae-d3nmtd5d/</t>
+          <t>https://alkhaterstore.com/product/mstn24crnag16-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d8%a7%d9%86%d9%81%d9%8a%d9%86%d8%aa%d9%8a-22000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1/</t>
         </is>
       </c>
       <c r="M147" t="n">
@@ -9459,18 +9521,22 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>AC07867</t>
+          <t>AC08261</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف امبيكس سبلت 21000 وحدة بارد-IM24S3CCSA FAN”</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
+          <t>“MSTN18CRNAG16 - مكيف ميديا انفينتي 18300 وحدة بارد جداري اسود”</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Midea</t>
+        </is>
+      </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>IM24S3CCSA</t>
+          <t>MSTN18CRNAG16</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -9492,17 +9558,17 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2749</v>
+        <v>3299</v>
       </c>
       <c r="J148" t="n">
-        <v>2749</v>
+        <v>3299</v>
       </c>
       <c r="K148" t="b">
         <v>0</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%85%d8%a8%d9%8a%d9%83%d8%b3-%d8%b3%d8%a8%d9%84%d8%aa-21000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-im24s3ccsa-fan/</t>
+          <t>https://alkhaterstore.com/product/mstn18crnag16-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d8%a7%d9%86%d9%81%d9%8a%d9%86%d8%aa%d9%8a-18300-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1/</t>
         </is>
       </c>
       <c r="M148" t="n">
@@ -9517,26 +9583,26 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AC08327</t>
+          <t>AC07795</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “هاير مكيف سبليت 27400 وحده 2.5 طن نانو واي فاي بارد - HSU-30LPC13/R2(T3)”</t>
+          <t>“مكيف سبليت وايت وستنجهاوس 18500 وحدة بارد واي فاي - WWS18G23WI”</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Haier</t>
+          <t>Westinghouse</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>HSU-30LPC13</t>
+          <t>WWS18G23WI</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -9554,17 +9620,17 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4999</v>
+        <v>2499</v>
       </c>
       <c r="J149" t="n">
-        <v>4999</v>
+        <v>2499</v>
       </c>
       <c r="K149" t="b">
         <v>0</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/hsu-30lpc13-r2t3/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%88%d8%a7%d9%8a%d8%aa-%d9%88%d8%b3%d8%aa%d9%86%d8%ac%d9%87%d8%a7%d9%88%d8%b3-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-18500-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-2/</t>
         </is>
       </c>
       <c r="M149" t="n">
@@ -9579,22 +9645,22 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AC08262</t>
+          <t>AC07797</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “MSTN24CRNAG16 - مكيف ميديا انفينتي 22000 وحدة بارد جداري اسود”</t>
+          <t>“مكيف سبلت يوركس 26800 وحدة بارد - YORX-30KC”</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Midea</t>
+          <t>Yorksa</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>MSTN24CRNAG16</t>
+          <t>YORX-30KC</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -9616,17 +9682,17 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3999</v>
+        <v>3899</v>
       </c>
       <c r="J150" t="n">
-        <v>3999</v>
+        <v>3899</v>
       </c>
       <c r="K150" t="b">
         <v>0</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/mstn24crnag16-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d8%a7%d9%86%d9%81%d9%8a%d9%86%d8%aa%d9%8a-22000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d8%aa-%d9%8a%d9%88%d8%b1%d9%83%d8%b3-26500-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-yorx-30kc/</t>
         </is>
       </c>
       <c r="M150" t="n">
@@ -9641,26 +9707,26 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>AC08261</t>
+          <t>AC04837</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “MSTN18CRNAG16 - مكيف ميديا انفينتي 18300 وحدة بارد جداري اسود”</t>
+          <t>“مكيف  ال ج فريش 21500وحدة بارد جداري - NF242C3SK”</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Midea</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MSTN18CRNAG16</t>
+          <t>NF242C3SK</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -9678,17 +9744,17 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3299</v>
+        <v>3899</v>
       </c>
       <c r="J151" t="n">
-        <v>3299</v>
+        <v>3899</v>
       </c>
       <c r="K151" t="b">
         <v>0</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/mstn18crnag16-%d9%85%d9%83%d9%8a%d9%81-%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d8%a7%d9%86%d9%81%d9%8a%d9%86%d8%aa%d9%8a-18300-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84-%d8%ac-%d9%81%d8%b1%d9%8a%d8%b4-21500%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-nf242c3sk/</t>
         </is>
       </c>
       <c r="M151" t="n">
@@ -9703,22 +9769,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>AC07795</t>
+          <t>AC04836</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف سبليت وايت وستنجهاوس 18500 وحدة بارد واي فاي - WWS18G23WI”</t>
+          <t>“مكيف ال ج فريش 18000 وحدة بارد جداري - NF182C2SK seer”</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Westinghouse</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>WWS18G23WI</t>
+          <t>NF182C2SK</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -9740,17 +9806,17 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2499</v>
+        <v>3299</v>
       </c>
       <c r="J152" t="n">
-        <v>2499</v>
+        <v>3299</v>
       </c>
       <c r="K152" t="b">
         <v>0</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%88%d8%a7%d9%8a%d8%aa-%d9%88%d8%b3%d8%aa%d9%86%d8%ac%d9%87%d8%a7%d9%88%d8%b3-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-18500-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-2/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84-%d8%ac-%d9%81%d8%b1%d9%8a%d8%b4-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-nf182c2sk-seer/</t>
         </is>
       </c>
       <c r="M152" t="n">
@@ -9765,18 +9831,22 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>AC07797</t>
+          <t>AC04391</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف سبلت يوركس 26800 وحدة بارد - YORX-30KC”</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>“مكيف الزامل سبليت 22000 وحدة بارد - MAZ24CCXAD1/MRZ24CDGCIAD1”</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Zamil</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>YORX-30KC</t>
+          <t>MAZ24CCXAD1</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -9798,17 +9868,17 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3899</v>
+        <v>3734</v>
       </c>
       <c r="J153" t="n">
-        <v>3899</v>
+        <v>3734</v>
       </c>
       <c r="K153" t="b">
         <v>0</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d8%aa-%d9%8a%d9%88%d8%b1%d9%83%d8%b3-26500-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-yorx-30kc/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84%d8%b2%d8%a7%d9%85%d9%84-22000-%d9%88%d8%ad%d8%af%d8%a9-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d8%a8%d8%a7%d8%b1%d8%af-maz24ccxad1-mrz24cdgciad1/</t>
         </is>
       </c>
       <c r="M153" t="n">
@@ -9823,26 +9893,26 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>AC04837</t>
+          <t>AC04390</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف  ال ج فريش 21500وحدة بارد جداري - NF242C3SK”</t>
+          <t>“مكيف الزامل سبليت 18000 وحدة بارد - MAZ18CCXAD”</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Zamil</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NF242C3SK</t>
+          <t>MAZ18CCXAD</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -9860,47 +9930,47 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3899</v>
+        <v>2894</v>
       </c>
       <c r="J154" t="n">
-        <v>3899</v>
+        <v>2894</v>
       </c>
       <c r="K154" t="b">
         <v>0</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84-%d8%ac-%d9%81%d8%b1%d9%8a%d8%b4-21500%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-nf242c3sk/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84%d8%b2%d8%a7%d9%85%d9%84-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
         </is>
       </c>
       <c r="M154" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-05-11 14:40</t>
+          <t>2026-05-11 14:41</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>AC04836</t>
+          <t>AC06072</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف ال ج فريش 18000 وحدة بارد جداري - NF182C2SK seer”</t>
+          <t>“ مكيف فريجو جلاكسي بلس 18400 وحدة بارد - سبليت  - FW18X2P22”</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Frigidaire</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NF182C2SK</t>
+          <t>FW18X2P22</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -9922,47 +9992,47 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3299</v>
+        <v>2339</v>
       </c>
       <c r="J155" t="n">
-        <v>3299</v>
+        <v>2339</v>
       </c>
       <c r="K155" t="b">
         <v>0</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84-%d8%ac-%d9%81%d8%b1%d9%8a%d8%b4-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-nf182c2sk-seer/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%81%d8%b1%d9%8a%d8%ac%d9%88-%d8%ac%d9%84%d8%a7%d9%83%d8%b3%d9%8a-%d8%a8%d9%84%d8%b3-18400-%d9%88%d8%ad%d8%af%d8%a9/</t>
         </is>
       </c>
       <c r="M155" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-05-11 14:40</t>
+          <t>2026-05-11 14:41</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AC04391</t>
+          <t>AC07796</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف الزامل سبليت 22000 وحدة بارد - MAZ24CCXAD1/MRZ24CDGCIAD1”</t>
+          <t>“مكيف سبليت وايت وستنجهاوس 22100 وحدة بارد - WWS24G23WC/I”</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Zamil</t>
+          <t>Westinghouse</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>MAZ24CCXAD1</t>
+          <t>WWS24G23WC</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -9984,51 +10054,47 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3734</v>
+        <v>3014</v>
       </c>
       <c r="J156" t="n">
-        <v>3734</v>
+        <v>3014</v>
       </c>
       <c r="K156" t="b">
         <v>0</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84%d8%b2%d8%a7%d9%85%d9%84-22000-%d9%88%d8%ad%d8%af%d8%a9-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d8%a8%d8%a7%d8%b1%d8%af-maz24ccxad1-mrz24cdgciad1/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%88%d8%a7%d9%8a%d8%aa-%d9%88%d8%b3%d8%aa%d9%86%d8%ac%d9%87%d8%a7%d9%88%d8%b3-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-22100-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af/</t>
         </is>
       </c>
       <c r="M156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-05-11 14:40</t>
+          <t>2026-05-11 14:41</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AC04390</t>
+          <t>AC07388</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف الزامل سبليت 18000 وحدة بارد - MAZ18CCXAD”</t>
+          <t>“يونيستار مكيف هواء سبليت - 26800 وحدة - بارد فقط - أبيض”</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Zamil</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>MAZ18CCXAD</t>
-        </is>
-      </c>
+          <t>Unistar</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -10046,17 +10112,17 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2894</v>
+        <v>3899</v>
       </c>
       <c r="J157" t="n">
-        <v>2894</v>
+        <v>3899</v>
       </c>
       <c r="K157" t="b">
         <v>0</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84%d8%b2%d8%a7%d9%85%d9%84-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
+          <t>https://alkhaterstore.com/product/%d9%8a%d9%88%d9%86%d9%8a%d8%b3%d8%aa%d8%a7%d8%b1-%d9%85%d9%83%d9%8a%d9%81-%d9%87%d9%88%d8%a7%d8%a1-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-26800-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%81/</t>
         </is>
       </c>
       <c r="M157" t="n">
@@ -10071,24 +10137,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AC06072</t>
+          <t>AC07385</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “ مكيف فريجو جلاكسي بلس 18400 وحدة بارد - سبليت  - FW18X2P22”</t>
+          <t>“مكيف يونيستار سبليت - 18000 وحدة بارد - UNST 18 CC”</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Frigidaire</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>FW18X2P22</t>
-        </is>
-      </c>
+          <t>Unistar</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
         <v>1.5</v>
       </c>
@@ -10108,17 +10170,17 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2339</v>
+        <v>1979</v>
       </c>
       <c r="J158" t="n">
-        <v>2339</v>
+        <v>1979</v>
       </c>
       <c r="K158" t="b">
         <v>0</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%81%d8%b1%d9%8a%d8%ac%d9%88-%d8%ac%d9%84%d8%a7%d9%83%d8%b3%d9%8a-%d8%a8%d9%84%d8%b3-18400-%d9%88%d8%ad%d8%af%d8%a9/</t>
+          <t>https://alkhaterstore.com/product/%d9%8a%d9%88%d9%86%d9%8a%d8%b3%d8%aa%d8%a7%d8%b1-%d9%85%d9%83%d9%8a%d9%81-%d9%87%d9%88%d8%a7%d8%a1-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%81/</t>
         </is>
       </c>
       <c r="M158" t="n">
@@ -10133,26 +10195,22 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AC07796</t>
+          <t>AC06421</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف سبليت وايت وستنجهاوس 22100 وحدة بارد - WWS24G23WC/I”</t>
+          <t>“ميديا اوول إيزي مكيف هواء سبليت مع تحكم واي فاي - 18500 وحدة - بارد فقط - أبيض”</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Westinghouse</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>WWS24G23WC</t>
-        </is>
-      </c>
+          <t>Midea</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -10170,17 +10228,17 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3014</v>
+        <v>2879</v>
       </c>
       <c r="J159" t="n">
-        <v>3014</v>
+        <v>2879</v>
       </c>
       <c r="K159" t="b">
         <v>0</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%88%d8%a7%d9%8a%d8%aa-%d9%88%d8%b3%d8%aa%d9%86%d8%ac%d9%87%d8%a7%d9%88%d8%b3-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-22100-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d8%a7%d9%88%d9%88%d9%84-%d8%a5%d9%8a%d8%b2%d9%8a-%d9%85%d9%83%d9%8a%d9%81-%d9%87%d9%88%d8%a7%d8%a1-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-%d9%85%d8%b9-%d8%aa%d8%ad%d9%83%d9%85/</t>
         </is>
       </c>
       <c r="M159" t="n">
@@ -10195,18 +10253,22 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AC07388</t>
+          <t>AC06288</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “يونيستار مكيف هواء سبليت - 26800 وحدة - بارد فقط - أبيض”</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
+          <t>“إل جي مكيف سبليت مع انفرتر أخضر - 20000 وحدة - بارد فقط - أبيض”</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -10224,17 +10286,17 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3899</v>
+        <v>3659</v>
       </c>
       <c r="J160" t="n">
-        <v>3899</v>
+        <v>3659</v>
       </c>
       <c r="K160" t="b">
         <v>0</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%8a%d9%88%d9%86%d9%8a%d8%b3%d8%aa%d8%a7%d8%b1-%d9%85%d9%83%d9%8a%d9%81-%d9%87%d9%88%d8%a7%d8%a1-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-26800-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%81/</t>
+          <t>https://alkhaterstore.com/product/%d8%a5%d9%84-%d8%ac%d9%8a-%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-%d9%85%d8%b9-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%a3%d8%ae%d8%b6%d8%b1-20000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8/</t>
         </is>
       </c>
       <c r="M160" t="n">
@@ -10249,15 +10311,19 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AC07385</t>
+          <t>AC06286</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف يونيستار سبليت - 18000 وحدة بارد - UNST 18 CC”</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
+          <t>“إل جي مكيف سبليت مع انفرتر أخضر - 17500 وحدة - بارد فقط - أبيض”</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
         <v>1.5</v>
@@ -10278,17 +10344,17 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1979</v>
+        <v>2939</v>
       </c>
       <c r="J161" t="n">
-        <v>1979</v>
+        <v>2939</v>
       </c>
       <c r="K161" t="b">
         <v>0</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%8a%d9%88%d9%86%d9%8a%d8%b3%d8%aa%d8%a7%d8%b1-%d9%85%d9%83%d9%8a%d9%81-%d9%87%d9%88%d8%a7%d8%a1-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%81/</t>
+          <t>https://alkhaterstore.com/product/%d8%a5%d9%84-%d8%ac%d9%8a-%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-%d9%85%d8%b9-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%a3%d8%ae%d8%b6%d8%b1-17500-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8/</t>
         </is>
       </c>
       <c r="M161" t="n">
@@ -10303,22 +10369,26 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AC06421</t>
+          <t>AC06017</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “ميديا اوول إيزي مكيف هواء سبليت مع تحكم واي فاي - 18500 وحدة - بارد فقط - أبيض”</t>
+          <t>“مكيف كرافت سبليت 11500 وحدة - بارد فقط - DSA12CE6YHA1”</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Midea</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Dansat</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>DSA12CE6YHA1</t>
+        </is>
+      </c>
       <c r="E162" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -10336,17 +10406,17 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2879</v>
+        <v>2099</v>
       </c>
       <c r="J162" t="n">
-        <v>2879</v>
+        <v>2099</v>
       </c>
       <c r="K162" t="b">
         <v>0</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%8a%d8%af%d9%8a%d8%a7-%d8%a7%d9%88%d9%88%d9%84-%d8%a5%d9%8a%d8%b2%d9%8a-%d9%85%d9%83%d9%8a%d9%81-%d9%87%d9%88%d8%a7%d8%a1-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-%d9%85%d8%b9-%d8%aa%d8%ad%d9%83%d9%85/</t>
+          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%83%d8%b1%d8%a7%d9%81%d8%aa-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-11500-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%81%d9%82%d8%b7-dsa12ce6yha1/</t>
         </is>
       </c>
       <c r="M162" t="n">
@@ -10361,16 +10431,24 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AC06288</t>
+          <t>AC05710</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “إل جي مكيف سبليت مع انفرتر أخضر - 20000 وحدة - بارد فقط - أبيض”</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
+          <t>“فريجو مكيف شباك 17200 وحدة - بارد فقط - أبيض - AC05710”</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Frigidaire</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>AC05710</t>
+        </is>
+      </c>
       <c r="E163" t="n">
         <v>1.5</v>
       </c>
@@ -10381,7 +10459,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10390,17 +10468,17 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3659</v>
+        <v>1559</v>
       </c>
       <c r="J163" t="n">
-        <v>3659</v>
+        <v>1559</v>
       </c>
       <c r="K163" t="b">
         <v>0</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d8%a5%d9%84-%d8%ac%d9%8a-%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-%d9%85%d8%b9-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%a3%d8%ae%d8%b6%d8%b1-20000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8/</t>
+          <t>https://alkhaterstore.com/product/%d9%81%d8%b1%d9%8a%d8%ac%d9%88-%d9%85%d9%83%d9%8a%d9%81-%d8%b4%d8%a8%d8%a7%d9%83-17200-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%81%d9%82%d8%b7-%d8%a3%d8%a8%d9%8a%d8%b6-ac05710/</t>
         </is>
       </c>
       <c r="M163" t="n">
@@ -10415,16 +10493,24 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AC06286</t>
+          <t>AC05905</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “إل جي مكيف سبليت مع انفرتر أخضر - 17500 وحدة - بارد فقط - أبيض”</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
+          <t>“مكيف جري 18000 وحدة بارد شباك - GJC18AG D3NMTD6D”</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>GJC18AG</t>
+        </is>
+      </c>
       <c r="E164" t="n">
         <v>1.5</v>
       </c>
@@ -10435,7 +10521,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10444,17 +10530,17 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2939</v>
+        <v>2039</v>
       </c>
       <c r="J164" t="n">
-        <v>2939</v>
+        <v>2039</v>
       </c>
       <c r="K164" t="b">
         <v>0</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d8%a5%d9%84-%d8%ac%d9%8a-%d9%85%d9%83%d9%8a%d9%81-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-%d9%85%d8%b9-%d8%a7%d9%86%d9%81%d8%b1%d8%aa%d8%b1-%d8%a3%d8%ae%d8%b6%d8%b1-17500-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8/</t>
+          <t>https://alkhaterstore.com/product/gjc18ag-d3nmtd6d-%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%b4%d8%a8%d8%a7%d9%83/</t>
         </is>
       </c>
       <c r="M164" t="n">
@@ -10469,26 +10555,26 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>AC06017</t>
+          <t>AC04867</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف كرافت سبليت 11500 وحدة - بارد فقط - DSA12CE6YHA1”</t>
+          <t>“ZCB18CAXFINNW مكيف الزامل شباك 17600 وحدة بارد”</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Dansat</t>
+          <t>Zamil</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>DSA12CE6YHA1</t>
+          <t>ZCB18CAXFINNW</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -10497,7 +10583,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10506,17 +10592,17 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2099</v>
+        <v>1859</v>
       </c>
       <c r="J165" t="n">
-        <v>2099</v>
+        <v>1859</v>
       </c>
       <c r="K165" t="b">
         <v>0</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%85%d9%83%d9%8a%d9%81-%d9%83%d8%b1%d8%a7%d9%81%d8%aa-%d8%b3%d8%a8%d9%84%d9%8a%d8%aa-11500-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%81%d9%82%d8%b7-dsa12ce6yha1/</t>
+          <t>https://alkhaterstore.com/product/zcb18caxfinnw-%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84%d8%b2%d8%a7%d9%85%d9%84-%d8%b4%d8%a8%d8%a7%d9%83-17600-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af/</t>
         </is>
       </c>
       <c r="M165" t="n">
@@ -10531,26 +10617,26 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AC05710</t>
+          <t>AC06420</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “فريجو مكيف شباك 17200 وحدة - بارد فقط - أبيض - AC05710”</t>
+          <t>“GVH60AP-D3DTC7A مكيف جري دولابي 51000 وحدة حار بارد”</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Frigidaire</t>
+          <t>Gree</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>AC05710</t>
+          <t>GVH60AP-D3DTC7A</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -10559,7 +10645,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10568,17 +10654,17 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1559</v>
+        <v>11738</v>
       </c>
       <c r="J166" t="n">
-        <v>1559</v>
+        <v>11738</v>
       </c>
       <c r="K166" t="b">
         <v>0</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/%d9%81%d8%b1%d9%8a%d8%ac%d9%88-%d9%85%d9%83%d9%8a%d9%81-%d8%b4%d8%a8%d8%a7%d9%83-17200-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d9%81%d9%82%d8%b7-%d8%a3%d8%a8%d9%8a%d8%b6-ac05710/</t>
+          <t>https://alkhaterstore.com/product/gvh60ap-d3dtc7a-%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%af%d9%88%d9%84%d8%a7%d8%a8%d9%8a-51000-%d9%88%d8%ad%d8%af%d8%a9-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af/</t>
         </is>
       </c>
       <c r="M166" t="n">
@@ -10593,26 +10679,26 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>AC05905</t>
+          <t>AC05907</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “مكيف جري 18000 وحدة بارد شباك - GJC18AG D3NMTD6D”</t>
+          <t>“GVC60AP-D3DTC7A مكيف جري 51000 وحدة بارد دولابي”</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Gree</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>GJC18AG</t>
+          <t>GVC60AP-D3DTC7A</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -10621,7 +10707,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10630,17 +10716,17 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2039</v>
+        <v>11378</v>
       </c>
       <c r="J167" t="n">
-        <v>2039</v>
+        <v>11378</v>
       </c>
       <c r="K167" t="b">
         <v>0</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/gjc18ag-d3nmtd6d-%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-18000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%b4%d8%a8%d8%a7%d9%83/</t>
+          <t>https://alkhaterstore.com/product/gvc60ap-d3dtc7a-%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-51000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%af%d9%88%d9%84%d8%a7%d8%a8%d9%8a/</t>
         </is>
       </c>
       <c r="M167" t="n">
@@ -10655,26 +10741,26 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>AC04867</t>
+          <t>AC06021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “ZCB18CAXFINNW مكيف الزامل شباك 17600 وحدة بارد”</t>
+          <t>“DSA36CE6YHA1 مكيف كرفت 31400 وحدة بارد جداري وطني”</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Zamil</t>
+          <t>Dansat</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>ZCB18CAXFINNW</t>
+          <t>DSA36CE6YHA1</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -10683,7 +10769,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Window</t>
+          <t>Split</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10692,17 +10778,17 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1859</v>
+        <v>4979</v>
       </c>
       <c r="J168" t="n">
-        <v>1859</v>
+        <v>4979</v>
       </c>
       <c r="K168" t="b">
         <v>0</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/zcb18caxfinnw-%d9%85%d9%83%d9%8a%d9%81-%d8%a7%d9%84%d8%b2%d8%a7%d9%85%d9%84-%d8%b4%d8%a8%d8%a7%d9%83-17600-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af/</t>
+          <t>https://alkhaterstore.com/product/dsa36ce6yha1-%d9%85%d9%83%d9%8a%d9%81-%d9%83%d8%b1%d9%81%d8%aa-31400-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d9%88%d8%b7%d9%86%d9%8a/</t>
         </is>
       </c>
       <c r="M168" t="n">
@@ -10717,26 +10803,26 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>AC06420</t>
+          <t>AC06020</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “GVH60AP-D3DTC7A مكيف جري دولابي 51000 وحدة حار بارد”</t>
+          <t>“DSA30CE6YHA1 بارد جداري SEER  مكيف كرفت 27200 وحدة”</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Dansat</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>GVH60AP-D3DTC7A</t>
+          <t>DSA30CE6YHA1</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -10754,17 +10840,17 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>11738</v>
+        <v>4259</v>
       </c>
       <c r="J169" t="n">
-        <v>11738</v>
+        <v>4259</v>
       </c>
       <c r="K169" t="b">
         <v>0</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/gvh60ap-d3dtc7a-%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-%d8%af%d9%88%d9%84%d8%a7%d8%a8%d9%8a-51000-%d9%88%d8%ad%d8%af%d8%a9-%d8%ad%d8%a7%d8%b1-%d8%a8%d8%a7%d8%b1%d8%af/</t>
+          <t>https://alkhaterstore.com/product/dsa30ce6yha1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-seer-%d9%85%d9%83%d9%8a%d9%81-%d9%83%d8%b1%d9%81%d8%aa-27200-%d9%88%d8%ad%d8%af%d8%a9/</t>
         </is>
       </c>
       <c r="M169" t="n">
@@ -10779,26 +10865,26 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AC05907</t>
+          <t>AC06019</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “GVC60AP-D3DTC7A مكيف جري 51000 وحدة بارد دولابي”</t>
+          <t>“DSA24CE6YHA1  بارد جداري SEER مكيف كرفت 23000 وحدة”</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Gree</t>
+          <t>Dansat</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>GVC60AP-D3DTC7A</t>
+          <t>DSA24CE6YHA1</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -10816,17 +10902,17 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>11378</v>
+        <v>3059</v>
       </c>
       <c r="J170" t="n">
-        <v>11378</v>
+        <v>3059</v>
       </c>
       <c r="K170" t="b">
         <v>0</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/gvc60ap-d3dtc7a-%d9%85%d9%83%d9%8a%d9%81-%d8%ac%d8%b1%d9%8a-51000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%af%d9%88%d9%84%d8%a7%d8%a8%d9%8a/</t>
+          <t>https://alkhaterstore.com/product/dsa24ce6yha1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-seer-%d9%85%d9%83%d9%8a%d9%81-%d9%83%d8%b1%d9%81%d8%aa-23000-%d9%88%d8%ad%d8%af%d8%a9/</t>
         </is>
       </c>
       <c r="M170" t="n">
@@ -10841,12 +10927,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>AC06021</t>
+          <t>AC06018</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “DSA36CE6YHA1 مكيف كرفت 31400 وحدة بارد جداري وطني”</t>
+          <t>“مكيف كرفت 17800 وحدة بارد جداري - DSA20CE6YHA1”</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10856,11 +10942,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>DSA36CE6YHA1</t>
+          <t>DSA20CE6YHA1</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -10878,17 +10964,17 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>4979</v>
+        <v>2299</v>
       </c>
       <c r="J171" t="n">
-        <v>4979</v>
+        <v>2299</v>
       </c>
       <c r="K171" t="b">
         <v>0</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/dsa36ce6yha1-%d9%85%d9%83%d9%8a%d9%81-%d9%83%d8%b1%d9%81%d8%aa-31400-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d9%88%d8%b7%d9%86%d9%8a/</t>
+          <t>https://alkhaterstore.com/product/dsa20ce6yha1-%d9%85%d9%83%d9%8a%d9%81-%d9%83%d8%b1%d9%81%d8%aa-17800-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d9%88%d8%b7%d9%86%d9%8a/</t>
         </is>
       </c>
       <c r="M171" t="n">
@@ -10903,26 +10989,26 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>AC06020</t>
+          <t>AC05571</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>إقرأ المزيد عن “DSA30CE6YHA1 بارد جداري SEER  مكيف كرفت 27200 وحدة”</t>
+          <t>“هاير مكيف 22000 وحدة بارد جداري - HSU-24LNX13/R2(T3)”</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Dansat</t>
+          <t>Haier</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DSA30CE6YHA1</t>
+          <t>HSU-24LNX13</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -10940,317 +11026,23 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4259</v>
+        <v>2819</v>
       </c>
       <c r="J172" t="n">
-        <v>4259</v>
+        <v>2819</v>
       </c>
       <c r="K172" t="b">
         <v>0</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>https://alkhaterstore.com/product/dsa30ce6yha1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-seer-%d9%85%d9%83%d9%8a%d9%81-%d9%83%d8%b1%d9%81%d8%aa-27200-%d9%88%d8%ad%d8%af%d8%a9/</t>
+          <t>https://alkhaterstore.com/product/hsu-24lnx13-r2t3-%d9%85%d9%83%d9%8a%d9%81-%d9%87%d8%a7%d9%8a%d8%b1-22000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
         </is>
       </c>
       <c r="M172" t="n">
         <v>8</v>
       </c>
       <c r="N172" t="inlineStr">
-        <is>
-          <t>2026-05-11 14:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>AC06019</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>إقرأ المزيد عن “DSA24CE6YHA1  بارد جداري SEER مكيف كرفت 23000 وحدة”</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Dansat</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>DSA24CE6YHA1</t>
-        </is>
-      </c>
-      <c r="E173" t="n">
-        <v>2</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Rotary</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Split</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="I173" t="n">
-        <v>3059</v>
-      </c>
-      <c r="J173" t="n">
-        <v>3059</v>
-      </c>
-      <c r="K173" t="b">
-        <v>0</v>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>https://alkhaterstore.com/product/dsa24ce6yha1-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-seer-%d9%85%d9%83%d9%8a%d9%81-%d9%83%d8%b1%d9%81%d8%aa-23000-%d9%88%d8%ad%d8%af%d8%a9/</t>
-        </is>
-      </c>
-      <c r="M173" t="n">
-        <v>8</v>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>2026-05-11 14:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>AC06018</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>إقرأ المزيد عن “مكيف كرفت 17800 وحدة بارد جداري - DSA20CE6YHA1”</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Dansat</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>DSA20CE6YHA1</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Rotary</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Split</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="I174" t="n">
-        <v>2299</v>
-      </c>
-      <c r="J174" t="n">
-        <v>2299</v>
-      </c>
-      <c r="K174" t="b">
-        <v>0</v>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>https://alkhaterstore.com/product/dsa20ce6yha1-%d9%85%d9%83%d9%8a%d9%81-%d9%83%d8%b1%d9%81%d8%aa-17800-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a-%d9%88%d8%b7%d9%86%d9%8a/</t>
-        </is>
-      </c>
-      <c r="M174" t="n">
-        <v>8</v>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>2026-05-11 14:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>AC05571</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>إقرأ المزيد عن “هاير مكيف 22000 وحدة بارد جداري - HSU-24LNX13/R2(T3)”</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Haier</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>HSU-24LNX13</t>
-        </is>
-      </c>
-      <c r="E175" t="n">
-        <v>2</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Rotary</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Split</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="I175" t="n">
-        <v>2819</v>
-      </c>
-      <c r="J175" t="n">
-        <v>2819</v>
-      </c>
-      <c r="K175" t="b">
-        <v>0</v>
-      </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>https://alkhaterstore.com/product/hsu-24lnx13-r2t3-%d9%85%d9%83%d9%8a%d9%81-%d9%87%d8%a7%d9%8a%d8%b1-22000-%d9%88%d8%ad%d8%af%d8%a9-%d8%a8%d8%a7%d8%b1%d8%af-%d8%ac%d8%af%d8%a7%d8%b1%d9%8a/</t>
-        </is>
-      </c>
-      <c r="M175" t="n">
-        <v>8</v>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>2026-05-11 14:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>AC06349</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>إقرأ المزيد عن “SUMO 75XL مكيف صحراوي سيمفوني 75 لتر”</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Rotary</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Split</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="I176" t="n">
-        <v>1199</v>
-      </c>
-      <c r="J176" t="n">
-        <v>1199</v>
-      </c>
-      <c r="K176" t="b">
-        <v>0</v>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>https://alkhaterstore.com/product/sumo-75xl-%d9%85%d9%83%d9%8a%d9%81-%d8%b5%d8%ad%d8%b1%d8%a7%d9%88%d9%8a-%d8%b3%d9%8a%d9%85%d9%81%d9%88%d9%86%d9%8a-75-%d9%84%d8%aa%d8%b1/</t>
-        </is>
-      </c>
-      <c r="M176" t="n">
-        <v>8</v>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>2026-05-11 14:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>AC06348</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>إقرأ المزيد عن “HICOOL i مكيف صحراوي سيمفوني 32 لتر”</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>HICOOL</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Rotary</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Split</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Cold</t>
-        </is>
-      </c>
-      <c r="I177" t="n">
-        <v>719</v>
-      </c>
-      <c r="J177" t="n">
-        <v>719</v>
-      </c>
-      <c r="K177" t="b">
-        <v>0</v>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>https://alkhaterstore.com/product/hicool-i-%d9%85%d9%83%d9%8a%d9%81-%d8%b5%d8%ad%d8%b1%d8%a7%d9%88%d9%8a-%d8%b3%d9%8a%d9%85%d9%81%d9%88%d9%86%d9%8a-32-%d9%84%d8%aa%d8%b1/</t>
-        </is>
-      </c>
-      <c r="M177" t="n">
-        <v>8</v>
-      </c>
-      <c r="N177" t="inlineStr">
         <is>
           <t>2026-05-11 14:41</t>
         </is>

--- a/price-tracking/channels/alkhater/alkhater_ac_prices.xlsx
+++ b/price-tracking/channels/alkhater/alkhater_ac_prices.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -586,7 +586,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -710,7 +710,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -772,7 +772,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1187,7 +1187,9 @@
           <t>WWA20K22R</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -1200,7 +1202,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1262,7 +1264,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1324,7 +1326,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1386,7 +1388,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1448,7 +1450,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1510,7 +1512,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1572,7 +1574,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1634,7 +1636,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1696,7 +1698,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1758,7 +1760,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1820,7 +1822,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1882,7 +1884,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1944,7 +1946,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -2006,7 +2008,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2068,7 +2070,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2130,7 +2132,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2192,7 +2194,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2254,7 +2256,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2316,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2378,7 +2380,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2440,7 +2442,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2502,7 +2504,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2564,7 +2566,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2621,12 +2623,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Portable</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2674,7 +2676,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2683,12 +2685,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Portable</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2750,7 +2752,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2812,7 +2814,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2874,7 +2876,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2936,7 +2938,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2998,7 +3000,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3060,7 +3062,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3122,7 +3124,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3184,7 +3186,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3246,7 +3248,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3308,7 +3310,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3370,7 +3372,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3427,12 +3429,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Portable</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3494,7 +3496,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3556,7 +3558,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3618,7 +3620,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3680,7 +3682,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3737,12 +3739,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Free Standing</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3804,7 +3806,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3866,7 +3868,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3928,7 +3930,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3990,7 +3992,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -4052,7 +4054,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -4114,7 +4116,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -4176,7 +4178,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -4238,7 +4240,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -4300,7 +4302,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -4362,7 +4364,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -4424,7 +4426,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -4486,7 +4488,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -4548,7 +4550,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -4610,7 +4612,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4657,7 +4659,9 @@
           <t>HW-18LME13</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>1.5</v>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -4670,7 +4674,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4732,7 +4736,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4794,7 +4798,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4856,7 +4860,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4918,7 +4922,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4976,7 +4980,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -5038,7 +5042,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -5100,7 +5104,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -5162,7 +5166,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -5224,7 +5228,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -5286,7 +5290,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -5348,7 +5352,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -5410,7 +5414,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -5472,7 +5476,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -5534,7 +5538,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -5596,7 +5600,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -5658,7 +5662,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -5720,7 +5724,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -5782,7 +5786,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -5844,7 +5848,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -5906,7 +5910,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -5968,7 +5972,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -6030,7 +6034,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -6092,7 +6096,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -6154,7 +6158,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -6216,7 +6220,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -6263,7 +6267,9 @@
           <t>LA242C0</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="n">
+        <v>2</v>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -6276,7 +6282,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -6338,7 +6344,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -6400,7 +6406,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -6462,7 +6468,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -6520,7 +6526,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -6582,7 +6588,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -6644,7 +6650,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -6706,7 +6712,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -6768,7 +6774,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -6830,7 +6836,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -6892,7 +6898,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -6954,7 +6960,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -7016,7 +7022,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -7078,7 +7084,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -7140,7 +7146,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -7202,7 +7208,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -7264,7 +7270,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -7326,7 +7332,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -7388,7 +7394,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -7450,7 +7456,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -7512,7 +7518,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -7574,7 +7580,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -7621,7 +7627,9 @@
           <t>DSA12C</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="n">
+        <v>1</v>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -7634,7 +7642,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -7696,7 +7704,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -7743,7 +7751,9 @@
           <t>FW12X2P22</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="n">
+        <v>1</v>
+      </c>
       <c r="F119" t="inlineStr">
         <is>
           <t>Rotary</t>
@@ -7756,7 +7766,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -7818,7 +7828,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -7880,7 +7890,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -7937,12 +7947,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Portable</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -8004,7 +8014,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -8066,7 +8076,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -8128,7 +8138,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -8190,7 +8200,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -8252,7 +8262,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -8314,7 +8324,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -8376,7 +8386,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -8438,7 +8448,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -8500,7 +8510,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -8562,7 +8572,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -8624,7 +8634,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -8686,7 +8696,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -8748,7 +8758,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -8810,7 +8820,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -8872,7 +8882,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -8934,7 +8944,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -8996,7 +9006,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -9058,7 +9068,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -9120,7 +9130,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -9182,7 +9192,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -9239,12 +9249,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Portable</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -9306,7 +9316,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -9368,7 +9378,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -9430,7 +9440,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -9492,7 +9502,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -9554,7 +9564,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -9616,7 +9626,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -9678,7 +9688,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -9740,7 +9750,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I151" t="n">
@@ -9802,7 +9812,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -9864,7 +9874,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -9926,7 +9936,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -9988,7 +9998,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -10050,7 +10060,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -10108,7 +10118,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I157" t="n">
@@ -10166,7 +10176,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -10224,7 +10234,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -10282,7 +10292,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I160" t="n">
@@ -10340,7 +10350,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -10402,7 +10412,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -10464,7 +10474,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -10526,7 +10536,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -10588,7 +10598,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I165" t="n">
@@ -10645,12 +10655,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Free Standing</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Heat &amp; Cool</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -10707,12 +10717,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Split</t>
+          <t>Free Standing</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -10774,7 +10784,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -10836,7 +10846,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -10898,7 +10908,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -10960,7 +10970,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -11022,7 +11032,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Cold</t>
+          <t>Cooling Only</t>
         </is>
       </c>
       <c r="I172" t="n">

--- a/price-tracking/channels/alkhater/alkhater_ac_prices.xlsx
+++ b/price-tracking/channels/alkhater/alkhater_ac_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N172"/>
+  <dimension ref="A1:P172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,16 @@
           <t>Scraped_At</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Discount_Pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>In_Stock</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -549,6 +559,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -611,6 +623,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,6 +687,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -735,6 +751,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -797,6 +815,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -859,6 +879,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -921,6 +943,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -983,6 +1007,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1045,6 +1071,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1103,6 +1131,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1165,6 +1195,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1227,6 +1259,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1289,6 +1323,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1351,6 +1387,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1413,6 +1451,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1475,6 +1515,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1537,6 +1579,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1599,6 +1643,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1661,6 +1707,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1723,6 +1771,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1785,6 +1835,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1847,6 +1899,8 @@
           <t>2026-05-11 14:38</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1909,6 +1963,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1971,6 +2027,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2033,6 +2091,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2095,6 +2155,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2157,6 +2219,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2219,6 +2283,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2281,6 +2347,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2343,6 +2411,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2405,6 +2475,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2467,6 +2539,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2529,6 +2603,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2591,6 +2667,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2653,6 +2731,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2715,6 +2795,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2777,6 +2859,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2839,6 +2923,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2901,6 +2987,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2963,6 +3051,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3025,6 +3115,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3087,6 +3179,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3149,6 +3243,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3211,6 +3307,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3273,6 +3371,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3335,6 +3435,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3397,6 +3499,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3459,6 +3563,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3521,6 +3627,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3583,6 +3691,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3645,6 +3755,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3707,6 +3819,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3769,6 +3883,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3831,6 +3947,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3893,6 +4011,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3955,6 +4075,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4017,6 +4139,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4079,6 +4203,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4141,6 +4267,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4203,6 +4331,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4265,6 +4395,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4327,6 +4459,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4389,6 +4523,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4451,6 +4587,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4513,6 +4651,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4575,6 +4715,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4637,6 +4779,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4699,6 +4843,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4761,6 +4907,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4823,6 +4971,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4885,6 +5035,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4947,6 +5099,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5005,6 +5159,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5067,6 +5223,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5129,6 +5287,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5191,6 +5351,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5253,6 +5415,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5315,6 +5479,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5377,6 +5543,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5439,6 +5607,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5501,6 +5671,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5563,6 +5735,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5625,6 +5799,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5687,6 +5863,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5749,6 +5927,8 @@
           <t>2026-05-11 14:39</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5811,6 +5991,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5873,6 +6055,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5935,6 +6119,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5997,6 +6183,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6059,6 +6247,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6121,6 +6311,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6183,6 +6375,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6245,6 +6439,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6307,6 +6503,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6369,6 +6567,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6431,6 +6631,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6493,6 +6695,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6551,6 +6755,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6613,6 +6819,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6675,6 +6883,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6737,6 +6947,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6799,6 +7011,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6861,6 +7075,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6923,6 +7139,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6985,6 +7203,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7047,6 +7267,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7109,6 +7331,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7171,6 +7395,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7233,6 +7459,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7295,6 +7523,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7357,6 +7587,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7419,6 +7651,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7481,6 +7715,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7543,6 +7779,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7605,6 +7843,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7667,6 +7907,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7729,6 +7971,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7791,6 +8035,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7853,6 +8099,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7915,6 +8163,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7977,6 +8227,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8039,6 +8291,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8101,6 +8355,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8163,6 +8419,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8225,6 +8483,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8287,6 +8547,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8349,6 +8611,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8411,6 +8675,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8473,6 +8739,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8535,6 +8803,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8597,6 +8867,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8659,6 +8931,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8721,6 +8995,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8783,6 +9059,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8845,6 +9123,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8907,6 +9187,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8969,6 +9251,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9031,6 +9315,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9093,6 +9379,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9155,6 +9443,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9217,6 +9507,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9279,6 +9571,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9341,6 +9635,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9403,6 +9699,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9465,6 +9763,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9527,6 +9827,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9589,6 +9891,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9651,6 +9955,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9713,6 +10019,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9775,6 +10083,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9837,6 +10147,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9899,6 +10211,8 @@
           <t>2026-05-11 14:40</t>
         </is>
       </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9961,6 +10275,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10023,6 +10339,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10085,6 +10403,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10143,6 +10463,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10201,6 +10523,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10259,6 +10583,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10317,6 +10643,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10375,6 +10703,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10437,6 +10767,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10499,6 +10831,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10561,6 +10895,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10623,6 +10959,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10685,6 +11023,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10747,6 +11087,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10809,6 +11151,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10871,6 +11215,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10933,6 +11279,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10995,6 +11343,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11057,6 +11407,8 @@
           <t>2026-05-11 14:41</t>
         </is>
       </c>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
